--- a/docs/d/79/inyear.xlsx
+++ b/docs/d/79/inyear.xlsx
@@ -12,7 +12,7 @@
     <sheet name="By Area" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$146</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 104 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 105 clubs short</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC145"/>
+  <dimension ref="A1:AC146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3700,11 +3700,11 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>28678381</v>
+        <v>28680804</v>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Strategic Gears Toastmasters Club</t>
+          <t>SEVEN Toastmasters</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
@@ -3722,25 +3722,25 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K30" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L30" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M30" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O30" s="7" t="inlineStr">
@@ -3781,12 +3781,10 @@
       <c r="Z30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA30" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" s="4" t="n">
-        <v>4</v>
-      </c>
+      <c r="AA30" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB30" s="4" t="n"/>
       <c r="AC30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
@@ -3797,15 +3795,15 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>925526</v>
+        <v>28678381</v>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Arabian Stallions Club</t>
+          <t>Strategic Gears Toastmasters Club</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
@@ -3823,25 +3821,25 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M31" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O31" s="7" t="inlineStr">
@@ -3850,7 +3848,7 @@
         </is>
       </c>
       <c r="P31" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q31" s="9" t="n">
         <v>0</v>
@@ -3868,13 +3866,13 @@
         <v>0</v>
       </c>
       <c r="V31" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X31" s="10" t="n">
-        <v>4</v>
+      <c r="X31" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y31" s="9" t="n">
         <v>0</v>
@@ -3882,8 +3880,8 @@
       <c r="Z31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA31" s="10" t="n">
-        <v>1</v>
+      <c r="AA31" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB31" s="4" t="n">
         <v>4</v>
@@ -3902,15 +3900,15 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>6569335</v>
+        <v>925526</v>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>PRERANA TOASTMASTERS CLUB</t>
+          <t>Arabian Stallions Club</t>
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F32" s="6" t="n">
         <v>10</v>
@@ -3924,13 +3922,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
@@ -3951,49 +3949,45 @@
         </is>
       </c>
       <c r="P32" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Q32" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="10" t="n">
+      <c r="W32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W32" s="10" t="n">
+      <c r="Y32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB32" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="X32" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA32" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB32" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC32" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+      <c r="AC32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -4007,15 +4001,15 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>2496</v>
+        <v>6569335</v>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Serendib Toastmasters Club</t>
+          <t>PRERANA TOASTMASTERS CLUB</t>
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>10</v>
@@ -4029,13 +4023,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
@@ -4056,16 +4050,16 @@
         </is>
       </c>
       <c r="P33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="Q33" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S33" s="9" t="n">
-        <v>1</v>
+      <c r="S33" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="T33" s="9" t="n">
         <v>0</v>
@@ -4076,25 +4070,29 @@
       <c r="V33" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W33" s="9" t="n">
-        <v>1</v>
+      <c r="W33" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X33" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z33" s="9" t="n">
-        <v>0</v>
+      <c r="Z33" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA33" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB33" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC33" s="4" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="AC33" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -4108,15 +4106,15 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>4476277</v>
+        <v>2496</v>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Wisdom Toastmasters Club</t>
+          <t>Serendib Toastmasters Club</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>10</v>
@@ -4130,17 +4128,17 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M34" s="8" t="n">
@@ -4160,13 +4158,13 @@
         <v>0</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S34" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T34" s="9" t="n">
         <v>0</v>
@@ -4174,50 +4172,50 @@
       <c r="U34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V34" s="9" t="n">
-        <v>0</v>
+      <c r="V34" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W34" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X34" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB34" s="4" t="n">
         <v>5</v>
-      </c>
-      <c r="Y34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA34" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB34" s="4" t="n">
-        <v>2</v>
       </c>
       <c r="AC34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1307541</v>
+        <v>4476277</v>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Asharqia Women Toastmasters Club</t>
+          <t>Wisdom Toastmasters Club</t>
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>10</v>
@@ -4231,17 +4229,17 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L35" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L35" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M35" s="8" t="n">
@@ -4258,7 +4256,7 @@
         </is>
       </c>
       <c r="P35" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q35" s="9" t="n">
         <v>0</v>
@@ -4275,26 +4273,26 @@
       <c r="U35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V35" s="10" t="n">
-        <v>4</v>
+      <c r="V35" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W35" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X35" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z35" s="10" t="n">
-        <v>1</v>
+      <c r="Z35" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA35" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB35" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AC35" s="4" t="inlineStr"/>
     </row>
@@ -4310,15 +4308,15 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>6485525</v>
+        <v>1307541</v>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Dammam Technology College Toastmasters Club</t>
+          <t>Asharqia Women Toastmasters Club</t>
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>10</v>
@@ -4332,25 +4330,25 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M36" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O36" s="7" t="inlineStr">
@@ -4359,7 +4357,7 @@
         </is>
       </c>
       <c r="P36" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q36" s="9" t="n">
         <v>0</v>
@@ -4376,26 +4374,26 @@
       <c r="U36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V36" s="9" t="n">
-        <v>0</v>
+      <c r="V36" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W36" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="X36" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z36" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA36" s="9" t="n">
-        <v>0</v>
+      <c r="Z36" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA36" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB36" s="4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AC36" s="4" t="inlineStr"/>
     </row>
@@ -4411,11 +4409,11 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>3888434</v>
+        <v>6485525</v>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Hajariat Explorer</t>
+          <t>Dammam Technology College Toastmasters Club</t>
         </is>
       </c>
       <c r="E37" s="5" t="n">
@@ -4433,10 +4431,10 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K37" s="4" t="n">
         <v>0</v>
@@ -4447,11 +4445,11 @@
         </is>
       </c>
       <c r="M37" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O37" s="7" t="inlineStr">
@@ -4483,8 +4481,8 @@
       <c r="W37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X37" s="10" t="n">
-        <v>4</v>
+      <c r="X37" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y37" s="9" t="n">
         <v>0</v>
@@ -4492,8 +4490,8 @@
       <c r="Z37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA37" s="10" t="n">
-        <v>1</v>
+      <c r="AA37" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB37" s="4" t="n">
         <v>2</v>
@@ -4512,11 +4510,11 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>7745277</v>
+        <v>3888434</v>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Khutwa</t>
+          <t>Hajariat Explorer</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
@@ -4537,10 +4535,10 @@
         <v>9</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
@@ -4579,7 +4577,7 @@
         <v>0</v>
       </c>
       <c r="V38" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W38" s="9" t="n">
         <v>0</v>
@@ -4597,7 +4595,7 @@
         <v>1</v>
       </c>
       <c r="AB38" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC38" s="4" t="inlineStr"/>
     </row>
@@ -4613,15 +4611,15 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>7113498</v>
+        <v>7745277</v>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>NABDH Toastmasters Club</t>
+          <t>Khutwa</t>
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>10</v>
@@ -4635,10 +4633,10 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>2</v>
@@ -4662,22 +4660,22 @@
         </is>
       </c>
       <c r="P39" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R39" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S39" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T39" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U39" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="T39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V39" s="9" t="n">
         <v>2</v>
@@ -4686,19 +4684,19 @@
         <v>0</v>
       </c>
       <c r="X39" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z39" s="10" t="n">
-        <v>1</v>
+      <c r="Z39" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA39" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB39" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AC39" s="4" t="inlineStr"/>
     </row>
@@ -4710,15 +4708,15 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>07</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>6798227</v>
+        <v>7113498</v>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Al Kalimah Gowh</t>
+          <t>NABDH Toastmasters Club</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
@@ -4736,17 +4734,17 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L40" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L40" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M40" s="8" t="n">
@@ -4763,43 +4761,43 @@
         </is>
       </c>
       <c r="P40" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R40" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S40" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W40" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="T40" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V40" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="W40" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X40" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y40" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA40" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB40" s="4" t="n">
         <v>6</v>
-      </c>
-      <c r="Y40" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z40" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA40" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB40" s="4" t="n">
-        <v>4</v>
       </c>
       <c r="AC40" s="4" t="inlineStr"/>
     </row>
@@ -4815,15 +4813,15 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>28678464</v>
+        <v>6798227</v>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>AlMashael</t>
+          <t>Al Kalimah Gowh</t>
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F41" s="6" t="n">
         <v>10</v>
@@ -4837,13 +4835,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -4863,50 +4861,46 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P41" s="10" t="n">
-        <v>5</v>
+      <c r="P41" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Q41" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S41" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T41" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U41" s="10" t="n">
-        <v>1</v>
+      <c r="S41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V41" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W41" s="9" t="n">
-        <v>1</v>
+      <c r="W41" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X41" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA41" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB41" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="Y41" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z41" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA41" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB41" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC41" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+      <c r="AC41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -4920,15 +4914,15 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>1427793</v>
+        <v>28678464</v>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>La'aLe'e Toastmasters</t>
+          <t>AlMashael</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -4942,17 +4936,17 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M42" s="8" t="n">
@@ -4968,32 +4962,32 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P42" s="9" t="n">
-        <v>0</v>
+      <c r="P42" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Q42" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S42" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" s="9" t="n">
-        <v>0</v>
+      <c r="S42" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T42" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V42" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W42" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X42" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y42" s="9" t="n">
         <v>0</v>
@@ -5005,9 +4999,13 @@
         <v>1</v>
       </c>
       <c r="AB42" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC42" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC42" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -5021,11 +5019,11 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>7030499</v>
+        <v>1427793</v>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>REHAB Toastmasters Club</t>
+          <t>La'aLe'e Toastmasters</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">
@@ -5043,10 +5041,10 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K43" s="4" t="n">
         <v>0</v>
@@ -5094,19 +5092,19 @@
         <v>0</v>
       </c>
       <c r="X43" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB43" s="4" t="n">
         <v>6</v>
-      </c>
-      <c r="Y43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA43" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB43" s="4" t="n">
-        <v>2</v>
       </c>
       <c r="AC43" s="4" t="inlineStr"/>
     </row>
@@ -5118,19 +5116,19 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>08</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>7864178</v>
+        <v>7030499</v>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Alnaseem</t>
+          <t>REHAB Toastmasters Club</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>10</v>
@@ -5144,13 +5142,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
@@ -5171,7 +5169,7 @@
         </is>
       </c>
       <c r="P44" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q44" s="9" t="n">
         <v>0</v>
@@ -5182,14 +5180,14 @@
       <c r="S44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T44" s="10" t="n">
-        <v>1</v>
+      <c r="T44" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U44" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V44" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W44" s="9" t="n">
         <v>0</v>
@@ -5207,7 +5205,7 @@
         <v>1</v>
       </c>
       <c r="AB44" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AC44" s="4" t="inlineStr"/>
     </row>
@@ -5223,15 +5221,15 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>7329169</v>
+        <v>7864178</v>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Alsalam</t>
+          <t>Alnaseem</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5248,10 +5246,10 @@
         <v>10</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -5272,7 +5270,7 @@
         </is>
       </c>
       <c r="P45" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q45" s="9" t="n">
         <v>0</v>
@@ -5283,32 +5281,32 @@
       <c r="S45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T45" s="9" t="n">
-        <v>0</v>
+      <c r="T45" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U45" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V45" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W45" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X45" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB45" s="4" t="n">
         <v>4</v>
-      </c>
-      <c r="Y45" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z45" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA45" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB45" s="4" t="n">
-        <v>3</v>
       </c>
       <c r="AC45" s="4" t="inlineStr"/>
     </row>
@@ -5324,11 +5322,11 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>1219742</v>
+        <v>7329169</v>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Danat Alkhaleej</t>
+          <t>Alsalam</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
@@ -5346,70 +5344,70 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="J46" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M46" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N46" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O46" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB46" s="4" t="n">
         <v>3</v>
-      </c>
-      <c r="J46" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M46" s="8" t="n">
-        <v>46387</v>
-      </c>
-      <c r="N46" s="4" t="inlineStr">
-        <is>
-          <t>Officer list on time</t>
-        </is>
-      </c>
-      <c r="O46" s="7" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P46" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W46" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X46" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y46" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z46" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA46" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB46" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="AC46" s="4" t="inlineStr"/>
     </row>
@@ -5425,11 +5423,11 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>6911242</v>
+        <v>1219742</v>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Manahel</t>
+          <t>Danat Alkhaleej</t>
         </is>
       </c>
       <c r="E47" s="5" t="n">
@@ -5447,10 +5445,10 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K47" s="4" t="n">
         <v>0</v>
@@ -5510,7 +5508,7 @@
         <v>0</v>
       </c>
       <c r="AB47" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC47" s="4" t="inlineStr"/>
     </row>
@@ -5526,11 +5524,11 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>2023097</v>
+        <v>6911242</v>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Qatif Oasis</t>
+          <t>Manahel</t>
         </is>
       </c>
       <c r="E48" s="5" t="n">
@@ -5548,13 +5546,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
@@ -5562,11 +5560,11 @@
         </is>
       </c>
       <c r="M48" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N48" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O48" s="7" t="inlineStr">
@@ -5593,13 +5591,13 @@
         <v>0</v>
       </c>
       <c r="V48" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X48" s="10" t="n">
-        <v>6</v>
+      <c r="X48" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y48" s="9" t="n">
         <v>0</v>
@@ -5607,11 +5605,11 @@
       <c r="Z48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA48" s="10" t="n">
-        <v>1</v>
+      <c r="AA48" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB48" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC48" s="4" t="inlineStr"/>
     </row>
@@ -5627,15 +5625,15 @@
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>7702173</v>
+        <v>2023097</v>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Raneem Toastmasters Club</t>
+          <t>Qatif Oasis</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5649,10 +5647,10 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J49" s="4" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="K49" s="4" t="n">
         <v>1</v>
@@ -5679,7 +5677,7 @@
         <v>0</v>
       </c>
       <c r="Q49" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R49" s="9" t="n">
         <v>0</v>
@@ -5700,25 +5698,21 @@
         <v>0</v>
       </c>
       <c r="X49" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z49" s="10" t="n">
-        <v>1</v>
+      <c r="Z49" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA49" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB49" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC49" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AC49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -5728,19 +5722,19 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>753319</v>
+        <v>7702173</v>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Al-Hasa Club</t>
+          <t>Raneem Toastmasters Club</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>10</v>
@@ -5754,13 +5748,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -5784,7 +5778,7 @@
         <v>0</v>
       </c>
       <c r="Q50" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R50" s="9" t="n">
         <v>0</v>
@@ -5799,27 +5793,31 @@
         <v>0</v>
       </c>
       <c r="V50" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W50" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X50" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z50" s="9" t="n">
-        <v>0</v>
+      <c r="Z50" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA50" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB50" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC50" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC50" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -5833,11 +5831,11 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>2412906</v>
+        <v>753319</v>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Athar Toastmasters Club</t>
+          <t>Al-Hasa Club</t>
         </is>
       </c>
       <c r="E51" s="5" t="n">
@@ -5855,13 +5853,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
@@ -5882,10 +5880,10 @@
         </is>
       </c>
       <c r="P51" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q51" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R51" s="9" t="n">
         <v>0</v>
@@ -5900,13 +5898,13 @@
         <v>0</v>
       </c>
       <c r="V51" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W51" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X51" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y51" s="9" t="n">
         <v>0</v>
@@ -5918,13 +5916,9 @@
         <v>1</v>
       </c>
       <c r="AB51" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC51" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AC51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
@@ -5938,11 +5932,11 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>6721954</v>
+        <v>2412906</v>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Danat Toastmasters Club</t>
+          <t>Athar Toastmasters Club</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
@@ -5960,13 +5954,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
@@ -5974,11 +5968,11 @@
         </is>
       </c>
       <c r="M52" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N52" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O52" s="7" t="inlineStr">
@@ -5987,10 +5981,10 @@
         </is>
       </c>
       <c r="P52" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q52" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R52" s="9" t="n">
         <v>0</v>
@@ -6005,13 +5999,13 @@
         <v>0</v>
       </c>
       <c r="V52" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X52" s="9" t="n">
-        <v>0</v>
+      <c r="X52" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y52" s="9" t="n">
         <v>0</v>
@@ -6019,13 +6013,17 @@
       <c r="Z52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA52" s="9" t="n">
-        <v>0</v>
+      <c r="AA52" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB52" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC52" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC52" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -6039,11 +6037,11 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>6643769</v>
+        <v>6721954</v>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Juwatha Toastmasters Club</t>
+          <t>Danat Toastmasters Club</t>
         </is>
       </c>
       <c r="E53" s="5" t="n">
@@ -6140,15 +6138,15 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>7370163</v>
+        <v>6643769</v>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Okadh Spirit</t>
+          <t>Juwatha Toastmasters Club</t>
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>10</v>
@@ -6162,10 +6160,10 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K54" s="4" t="n">
         <v>0</v>
@@ -6176,11 +6174,11 @@
         </is>
       </c>
       <c r="M54" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N54" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O54" s="7" t="inlineStr">
@@ -6197,8 +6195,8 @@
       <c r="R54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S54" s="10" t="n">
-        <v>2</v>
+      <c r="S54" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="T54" s="9" t="n">
         <v>0</v>
@@ -6212,8 +6210,8 @@
       <c r="W54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X54" s="10" t="n">
-        <v>5</v>
+      <c r="X54" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y54" s="9" t="n">
         <v>0</v>
@@ -6221,11 +6219,11 @@
       <c r="Z54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA54" s="10" t="n">
-        <v>1</v>
+      <c r="AA54" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB54" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC54" s="4" t="inlineStr"/>
     </row>
@@ -6241,11 +6239,11 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>7370520</v>
+        <v>7370163</v>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Sparks Toastmasters</t>
+          <t>Okadh Spirit</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">
@@ -6263,17 +6261,17 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L55" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L55" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M55" s="8" t="n">
@@ -6298,8 +6296,8 @@
       <c r="R55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S55" s="9" t="n">
-        <v>0</v>
+      <c r="S55" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T55" s="9" t="n">
         <v>0</v>
@@ -6308,25 +6306,25 @@
         <v>0</v>
       </c>
       <c r="V55" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W55" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X55" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z55" s="10" t="n">
-        <v>1</v>
+      <c r="Z55" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA55" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB55" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AC55" s="4" t="inlineStr"/>
     </row>
@@ -6338,19 +6336,19 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>47</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>1267758</v>
+        <v>7370520</v>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Asharqia Chamber Toastmasters</t>
+          <t>Sparks Toastmasters</t>
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>10</v>
@@ -6364,13 +6362,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J56" s="4" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
@@ -6408,26 +6406,26 @@
       <c r="U56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V56" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W56" s="10" t="n">
+      <c r="V56" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W56" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="X56" s="10" t="n">
-        <v>5</v>
-      </c>
       <c r="Y56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z56" s="9" t="n">
-        <v>0</v>
+      <c r="Z56" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA56" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB56" s="4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AC56" s="4" t="inlineStr"/>
     </row>
@@ -6443,15 +6441,15 @@
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>2523088</v>
+        <v>1267758</v>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Bloom Toastmasters</t>
+          <t>Asharqia Chamber Toastmasters</t>
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6465,17 +6463,17 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>10</v>
+      </c>
+      <c r="L57" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M57" s="8" t="n">
@@ -6492,10 +6490,10 @@
         </is>
       </c>
       <c r="P57" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q57" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R57" s="9" t="n">
         <v>0</v>
@@ -6509,11 +6507,11 @@
       <c r="U57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V57" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W57" s="9" t="n">
-        <v>0</v>
+      <c r="V57" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W57" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X57" s="10" t="n">
         <v>5</v>
@@ -6528,7 +6526,7 @@
         <v>1</v>
       </c>
       <c r="AB57" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC57" s="4" t="inlineStr"/>
     </row>
@@ -6544,11 +6542,11 @@
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>3358910</v>
+        <v>2523088</v>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Kalemat</t>
+          <t>Bloom Toastmasters</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
@@ -6566,25 +6564,25 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="K58" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L58" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L58" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M58" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N58" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O58" s="7" t="inlineStr">
@@ -6593,10 +6591,10 @@
         </is>
       </c>
       <c r="P58" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q58" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R58" s="9" t="n">
         <v>0</v>
@@ -6616,8 +6614,8 @@
       <c r="W58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X58" s="9" t="n">
-        <v>0</v>
+      <c r="X58" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y58" s="9" t="n">
         <v>0</v>
@@ -6625,17 +6623,13 @@
       <c r="Z58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA58" s="9" t="n">
-        <v>0</v>
+      <c r="AA58" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB58" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC58" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AC58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -6649,11 +6643,11 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>1068334</v>
+        <v>3358910</v>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>OKADH</t>
+          <t>Kalemat</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">
@@ -6671,17 +6665,17 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="J59" s="4" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="K59" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L59" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L59" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M59" s="8" t="n">
@@ -6722,7 +6716,7 @@
         <v>0</v>
       </c>
       <c r="X59" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y59" s="9" t="n">
         <v>0</v>
@@ -6734,9 +6728,13 @@
         <v>0</v>
       </c>
       <c r="AB59" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC59" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AC59" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -6750,11 +6748,11 @@
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>6051628</v>
+        <v>1068334</v>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Resala</t>
+          <t>OKADH</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
@@ -6775,10 +6773,10 @@
         <v>8</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
@@ -6786,11 +6784,11 @@
         </is>
       </c>
       <c r="M60" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N60" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O60" s="7" t="inlineStr">
@@ -6817,13 +6815,13 @@
         <v>0</v>
       </c>
       <c r="V60" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X60" s="10" t="n">
-        <v>4</v>
+      <c r="X60" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y60" s="9" t="n">
         <v>0</v>
@@ -6831,31 +6829,31 @@
       <c r="Z60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA60" s="10" t="n">
-        <v>1</v>
+      <c r="AA60" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB60" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AC60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>71</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>1357359</v>
+        <v>6051628</v>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Alif Advanced Toastmasters</t>
+          <t>Resala</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
@@ -6873,13 +6871,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J61" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -6918,25 +6916,25 @@
         <v>0</v>
       </c>
       <c r="V61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W61" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X61" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y61" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB61" s="4" t="n">
         <v>5</v>
-      </c>
-      <c r="Y61" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z61" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA61" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB61" s="4" t="n">
-        <v>2</v>
       </c>
       <c r="AC61" s="4" t="inlineStr"/>
     </row>
@@ -6952,15 +6950,15 @@
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>1009364</v>
+        <v>1357359</v>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Discovery Toastmasters Club</t>
+          <t>Alif Advanced Toastmasters</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -6974,17 +6972,17 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L62" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L62" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M62" s="8" t="n">
@@ -7001,7 +6999,7 @@
         </is>
       </c>
       <c r="P62" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q62" s="9" t="n">
         <v>0</v>
@@ -7010,34 +7008,34 @@
         <v>0</v>
       </c>
       <c r="S62" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T62" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T62" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U62" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V62" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W62" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X62" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z62" s="10" t="n">
-        <v>1</v>
+      <c r="Z62" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA62" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB62" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AC62" s="4" t="inlineStr"/>
     </row>
@@ -7053,15 +7051,15 @@
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>2807848</v>
+        <v>1009364</v>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Madhuram Malayalam Toastmasters Club</t>
+          <t>Discovery Toastmasters Club</t>
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -7075,17 +7073,17 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="J63" s="4" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>3</v>
+      </c>
+      <c r="L63" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M63" s="8" t="n">
@@ -7102,7 +7100,7 @@
         </is>
       </c>
       <c r="P63" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q63" s="9" t="n">
         <v>0</v>
@@ -7111,34 +7109,34 @@
         <v>0</v>
       </c>
       <c r="S63" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T63" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T63" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U63" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V63" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W63" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X63" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z63" s="9" t="n">
-        <v>0</v>
+      <c r="Z63" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA63" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB63" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AC63" s="4" t="inlineStr"/>
     </row>
@@ -7154,11 +7152,11 @@
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>4549879</v>
+        <v>2807848</v>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Orion Toastmasters Club</t>
+          <t>Madhuram Malayalam Toastmasters Club</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">
@@ -7176,10 +7174,10 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K64" s="4" t="n">
         <v>0</v>
@@ -7239,7 +7237,7 @@
         <v>1</v>
       </c>
       <c r="AB64" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AC64" s="4" t="inlineStr"/>
     </row>
@@ -7251,15 +7249,15 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>3281462</v>
+        <v>4549879</v>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Al Khobar Tamil Toastmasters Club</t>
+          <t>Orion Toastmasters Club</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">
@@ -7277,17 +7275,17 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="J65" s="4" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="K65" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L65" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L65" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M65" s="8" t="n">
@@ -7304,7 +7302,7 @@
         </is>
       </c>
       <c r="P65" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q65" s="9" t="n">
         <v>0</v>
@@ -7328,7 +7326,7 @@
         <v>0</v>
       </c>
       <c r="X65" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y65" s="9" t="n">
         <v>0</v>
@@ -7340,13 +7338,9 @@
         <v>1</v>
       </c>
       <c r="AB65" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC65" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AC65" s="4" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
@@ -7360,11 +7354,11 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>1895343</v>
+        <v>3281462</v>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>ERAM TOASTMASTERS CLUB</t>
+          <t>Al Khobar Tamil Toastmasters Club</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
@@ -7382,25 +7376,25 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="K66" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L66" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L66" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M66" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N66" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O66" s="7" t="inlineStr">
@@ -7409,7 +7403,7 @@
         </is>
       </c>
       <c r="P66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q66" s="9" t="n">
         <v>0</v>
@@ -7441,13 +7435,17 @@
       <c r="Z66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA66" s="9" t="n">
-        <v>0</v>
+      <c r="AA66" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB66" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC66" s="4" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="AC66" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
@@ -7461,11 +7459,11 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>28678091</v>
+        <v>1895343</v>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>FAL Toastmasters Club</t>
+          <t>ERAM TOASTMASTERS CLUB</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">
@@ -7483,10 +7481,10 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J67" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K67" s="4" t="n">
         <v>0</v>
@@ -7533,8 +7531,8 @@
       <c r="W67" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X67" s="9" t="n">
-        <v>0</v>
+      <c r="X67" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y67" s="9" t="n">
         <v>0</v>
@@ -7546,7 +7544,7 @@
         <v>0</v>
       </c>
       <c r="AB67" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC67" s="4" t="inlineStr"/>
     </row>
@@ -7562,11 +7560,11 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>1097255</v>
+        <v>28678091</v>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Horizon Toastmasters Club</t>
+          <t>FAL Toastmasters Club</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
@@ -7584,10 +7582,10 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K68" s="4" t="n">
         <v>0</v>
@@ -7598,11 +7596,11 @@
         </is>
       </c>
       <c r="M68" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N68" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O68" s="7" t="inlineStr">
@@ -7634,8 +7632,8 @@
       <c r="W68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X68" s="10" t="n">
-        <v>5</v>
+      <c r="X68" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y68" s="9" t="n">
         <v>0</v>
@@ -7643,11 +7641,11 @@
       <c r="Z68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA68" s="10" t="n">
-        <v>1</v>
+      <c r="AA68" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB68" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AC68" s="4" t="inlineStr"/>
     </row>
@@ -7663,11 +7661,11 @@
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>4757688</v>
+        <v>1097255</v>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>SLFE Toastmasters Club</t>
+          <t>Horizon Toastmasters Club</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">
@@ -7685,17 +7683,17 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="J69" s="4" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="K69" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L69" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L69" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M69" s="8" t="n">
@@ -7748,7 +7746,7 @@
         <v>1</v>
       </c>
       <c r="AB69" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AC69" s="4" t="inlineStr"/>
     </row>
@@ -7760,15 +7758,15 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>7828761</v>
+        <v>4757688</v>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>ABT Jaguar</t>
+          <t>SLFE Toastmasters Club</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
@@ -7786,25 +7784,25 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="K70" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L70" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L70" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M70" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N70" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O70" s="7" t="inlineStr">
@@ -7836,8 +7834,8 @@
       <c r="W70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X70" s="9" t="n">
-        <v>0</v>
+      <c r="X70" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y70" s="9" t="n">
         <v>0</v>
@@ -7845,11 +7843,11 @@
       <c r="Z70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA70" s="9" t="n">
-        <v>0</v>
+      <c r="AA70" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB70" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC70" s="4" t="inlineStr"/>
     </row>
@@ -7865,11 +7863,11 @@
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>918581</v>
+        <v>7828761</v>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>COSMOS</t>
+          <t>ABT Jaguar</t>
         </is>
       </c>
       <c r="E71" s="5" t="n">
@@ -7887,10 +7885,10 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J71" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K71" s="4" t="n">
         <v>0</v>
@@ -7901,11 +7899,11 @@
         </is>
       </c>
       <c r="M71" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N71" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O71" s="7" t="inlineStr">
@@ -7937,8 +7935,8 @@
       <c r="W71" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X71" s="10" t="n">
-        <v>5</v>
+      <c r="X71" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y71" s="9" t="n">
         <v>0</v>
@@ -7946,11 +7944,11 @@
       <c r="Z71" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA71" s="10" t="n">
-        <v>1</v>
+      <c r="AA71" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB71" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AC71" s="4" t="inlineStr"/>
     </row>
@@ -7966,11 +7964,11 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>7013378</v>
+        <v>918581</v>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Perlas Ng Silangan Toastmasters</t>
+          <t>COSMOS</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">
@@ -7988,10 +7986,10 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K72" s="4" t="n">
         <v>0</v>
@@ -8002,11 +8000,11 @@
         </is>
       </c>
       <c r="M72" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N72" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O72" s="7" t="inlineStr">
@@ -8038,8 +8036,8 @@
       <c r="W72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X72" s="9" t="n">
-        <v>0</v>
+      <c r="X72" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y72" s="9" t="n">
         <v>0</v>
@@ -8047,11 +8045,11 @@
       <c r="Z72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA72" s="9" t="n">
-        <v>0</v>
+      <c r="AA72" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB72" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AC72" s="4" t="inlineStr"/>
     </row>
@@ -8067,15 +8065,15 @@
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>7468427</v>
+        <v>7013378</v>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Telugu Toastmasters Club</t>
+          <t>Perlas Ng Silangan Toastmasters</t>
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -8089,10 +8087,10 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K73" s="4" t="n">
         <v>0</v>
@@ -8103,11 +8101,11 @@
         </is>
       </c>
       <c r="M73" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N73" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O73" s="7" t="inlineStr">
@@ -8139,20 +8137,20 @@
       <c r="W73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X73" s="10" t="n">
-        <v>5</v>
+      <c r="X73" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z73" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA73" s="10" t="n">
-        <v>1</v>
+      <c r="Z73" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA73" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB73" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AC73" s="4" t="inlineStr"/>
     </row>
@@ -8168,11 +8166,11 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>28677865</v>
+        <v>7468427</v>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>UADC Toastmasters Club</t>
+          <t>Telugu Toastmasters Club</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">
@@ -8190,17 +8188,17 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K74" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L74" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L74" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M74" s="8" t="n">
@@ -8216,8 +8214,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P74" s="10" t="n">
-        <v>4</v>
+      <c r="P74" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Q74" s="9" t="n">
         <v>0</v>
@@ -8241,19 +8239,19 @@
         <v>0</v>
       </c>
       <c r="X74" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y74" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA74" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB74" s="4" t="n">
         <v>6</v>
-      </c>
-      <c r="Y74" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z74" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA74" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB74" s="4" t="n">
-        <v>3</v>
       </c>
       <c r="AC74" s="4" t="inlineStr"/>
     </row>
@@ -8269,15 +8267,15 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>28680060</v>
+        <v>28677865</v>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>WMC Al-Khobar Toastmasters Club</t>
+          <t>UADC Toastmasters Club</t>
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F75" s="6" t="n">
         <v>10</v>
@@ -8291,10 +8289,10 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J75" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K75" s="4" t="n">
         <v>0</v>
@@ -8317,8 +8315,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P75" s="9" t="n">
-        <v>0</v>
+      <c r="P75" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q75" s="9" t="n">
         <v>0</v>
@@ -8342,7 +8340,7 @@
         <v>0</v>
       </c>
       <c r="X75" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y75" s="9" t="n">
         <v>0</v>
@@ -8354,7 +8352,7 @@
         <v>1</v>
       </c>
       <c r="AB75" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC75" s="4" t="inlineStr"/>
     </row>
@@ -8366,15 +8364,15 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>3337827</v>
+        <v>28680060</v>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Harmony Toastmasters Club</t>
+          <t>WMC Al-Khobar Toastmasters Club</t>
         </is>
       </c>
       <c r="E76" s="5" t="n">
@@ -8392,17 +8390,17 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="K76" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L76" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L76" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M76" s="8" t="n">
@@ -8443,7 +8441,7 @@
         <v>0</v>
       </c>
       <c r="X76" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y76" s="9" t="n">
         <v>0</v>
@@ -8455,7 +8453,7 @@
         <v>1</v>
       </c>
       <c r="AB76" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC76" s="4" t="inlineStr"/>
     </row>
@@ -8471,15 +8469,15 @@
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>1014428</v>
+        <v>3337827</v>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Nesma and Partners Toastmasters Club</t>
+          <t>Harmony Toastmasters Club</t>
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8493,17 +8491,17 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="K77" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L77" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L77" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M77" s="8" t="n">
@@ -8523,7 +8521,7 @@
         <v>0</v>
       </c>
       <c r="Q77" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R77" s="9" t="n">
         <v>0</v>
@@ -8549,20 +8547,16 @@
       <c r="Y77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z77" s="10" t="n">
-        <v>1</v>
+      <c r="Z77" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA77" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB77" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC77" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AC77" s="4" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
@@ -8576,15 +8570,15 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>28678946</v>
+        <v>1014428</v>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Pratham Hindi Toastmasters Club-KSA</t>
+          <t>Nesma and Partners Toastmasters Club</t>
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8598,17 +8592,17 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="K78" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L78" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L78" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M78" s="8" t="n">
@@ -8628,7 +8622,7 @@
         <v>0</v>
       </c>
       <c r="Q78" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R78" s="9" t="n">
         <v>0</v>
@@ -8649,21 +8643,25 @@
         <v>0</v>
       </c>
       <c r="X78" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y78" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z78" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA78" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB78" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="Y78" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z78" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA78" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB78" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC78" s="4" t="inlineStr"/>
+      <c r="AC78" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -8677,11 +8675,11 @@
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>28676546</v>
+        <v>28678946</v>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Voice Amplifiers</t>
+          <t>Pratham Hindi Toastmasters Club-KSA</t>
         </is>
       </c>
       <c r="E79" s="5" t="n">
@@ -8762,27 +8760,27 @@
         <v>1</v>
       </c>
       <c r="AB79" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC79" s="4" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>61</t>
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>7752813</v>
+        <v>28676546</v>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Empower Ladies Toastmasters Club</t>
+          <t>Voice Amplifiers</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">
@@ -8850,8 +8848,8 @@
       <c r="W80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X80" s="9" t="n">
-        <v>0</v>
+      <c r="X80" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y80" s="9" t="n">
         <v>0</v>
@@ -8863,7 +8861,7 @@
         <v>1</v>
       </c>
       <c r="AB80" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC80" s="4" t="inlineStr"/>
     </row>
@@ -8879,11 +8877,11 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>28677288</v>
+        <v>7752813</v>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>IBN Zahr Toastmasters Club</t>
+          <t>Empower Ladies Toastmasters Club</t>
         </is>
       </c>
       <c r="E81" s="5" t="n">
@@ -8901,25 +8899,25 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="K81" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L81" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L81" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M81" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N81" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O81" s="7" t="inlineStr">
@@ -8957,14 +8955,14 @@
       <c r="Y81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z81" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA81" s="9" t="n">
-        <v>0</v>
+      <c r="Z81" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA81" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB81" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC81" s="4" t="inlineStr"/>
     </row>
@@ -8980,11 +8978,11 @@
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>2094259</v>
+        <v>28677288</v>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Jubail Tamil Toastmasters Club</t>
+          <t>IBN Zahr Toastmasters Club</t>
         </is>
       </c>
       <c r="E82" s="5" t="n">
@@ -9002,25 +9000,25 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="K82" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L82" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L82" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M82" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N82" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O82" s="7" t="inlineStr">
@@ -9052,20 +9050,20 @@
       <c r="W82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X82" s="10" t="n">
-        <v>4</v>
+      <c r="X82" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z82" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA82" s="10" t="n">
-        <v>1</v>
+      <c r="Z82" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA82" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB82" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC82" s="4" t="inlineStr"/>
     </row>
@@ -9081,15 +9079,15 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>7717440</v>
+        <v>2094259</v>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>MIND Academy Toastmasters Club</t>
+          <t>Jubail Tamil Toastmasters Club</t>
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F83" s="6" t="n">
         <v>10</v>
@@ -9103,10 +9101,10 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K83" s="4" t="n">
         <v>0</v>
@@ -9130,22 +9128,22 @@
         </is>
       </c>
       <c r="P83" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q83" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R83" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="S83" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T83" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U83" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q83" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U83" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V83" s="9" t="n">
         <v>0</v>
@@ -9166,7 +9164,7 @@
         <v>1</v>
       </c>
       <c r="AB83" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AC83" s="4" t="inlineStr"/>
     </row>
@@ -9178,19 +9176,19 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>6854579</v>
+        <v>7717440</v>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Elite Stars Toastmasters Club</t>
+          <t>MIND Academy Toastmasters Club</t>
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -9204,10 +9202,10 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J84" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K84" s="4" t="n">
         <v>0</v>
@@ -9231,22 +9229,22 @@
         </is>
       </c>
       <c r="P84" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q84" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R84" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S84" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T84" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U84" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="Q84" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R84" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S84" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T84" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U84" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V84" s="9" t="n">
         <v>0</v>
@@ -9267,7 +9265,7 @@
         <v>1</v>
       </c>
       <c r="AB84" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AC84" s="4" t="inlineStr"/>
     </row>
@@ -9283,11 +9281,11 @@
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>2990</v>
+        <v>6854579</v>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>ELITE Toastmasters Club</t>
+          <t>Elite Stars Toastmasters Club</t>
         </is>
       </c>
       <c r="E85" s="5" t="n">
@@ -9368,7 +9366,7 @@
         <v>1</v>
       </c>
       <c r="AB85" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC85" s="4" t="inlineStr"/>
     </row>
@@ -9384,11 +9382,11 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>2469823</v>
+        <v>2990</v>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Farabi Toastmasters Club</t>
+          <t>ELITE Toastmasters Club</t>
         </is>
       </c>
       <c r="E86" s="5" t="n">
@@ -9406,10 +9404,10 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K86" s="4" t="n">
         <v>0</v>
@@ -9420,11 +9418,11 @@
         </is>
       </c>
       <c r="M86" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N86" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O86" s="7" t="inlineStr">
@@ -9456,8 +9454,8 @@
       <c r="W86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X86" s="9" t="n">
-        <v>0</v>
+      <c r="X86" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y86" s="9" t="n">
         <v>0</v>
@@ -9465,8 +9463,8 @@
       <c r="Z86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA86" s="9" t="n">
-        <v>0</v>
+      <c r="AA86" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB86" s="4" t="n">
         <v>2</v>
@@ -9485,11 +9483,11 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>7756528</v>
+        <v>2469823</v>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>FDC Toastmasters Club</t>
+          <t>Farabi Toastmasters Club</t>
         </is>
       </c>
       <c r="E87" s="5" t="n">
@@ -9507,10 +9505,10 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K87" s="4" t="n">
         <v>0</v>
@@ -9582,15 +9580,15 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>5177604</v>
+        <v>7756528</v>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Darvico Toastmasters Club</t>
+          <t>FDC Toastmasters Club</t>
         </is>
       </c>
       <c r="E88" s="5" t="n">
@@ -9608,10 +9606,10 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J88" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K88" s="4" t="n">
         <v>0</v>
@@ -9622,11 +9620,11 @@
         </is>
       </c>
       <c r="M88" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N88" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O88" s="7" t="inlineStr">
@@ -9658,8 +9656,8 @@
       <c r="W88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X88" s="10" t="n">
-        <v>5</v>
+      <c r="X88" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y88" s="9" t="n">
         <v>0</v>
@@ -9667,8 +9665,8 @@
       <c r="Z88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA88" s="10" t="n">
-        <v>1</v>
+      <c r="AA88" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB88" s="4" t="n">
         <v>2</v>
@@ -9687,15 +9685,15 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>8076</v>
+        <v>5177604</v>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Jubail Toastmasters Club</t>
+          <t>Darvico Toastmasters Club</t>
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9709,17 +9707,17 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="J89" s="4" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L89" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L89" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M89" s="8" t="n">
@@ -9747,17 +9745,17 @@
       <c r="S89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T89" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U89" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V89" s="10" t="n">
-        <v>4</v>
+      <c r="T89" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U89" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V89" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W89" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X89" s="10" t="n">
         <v>5</v>
@@ -9765,14 +9763,14 @@
       <c r="Y89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z89" s="10" t="n">
-        <v>1</v>
+      <c r="Z89" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA89" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB89" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AC89" s="4" t="inlineStr"/>
     </row>
@@ -9788,15 +9786,15 @@
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>6806730</v>
+        <v>8076</v>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>NISA - The Pride of Jubail Toastmasters Club</t>
+          <t>Jubail Toastmasters Club</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -9810,17 +9808,17 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="J90" s="4" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L90" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M90" s="8" t="n">
@@ -9848,32 +9846,32 @@
       <c r="S90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T90" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U90" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V90" s="9" t="n">
-        <v>0</v>
+      <c r="T90" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U90" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V90" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W90" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X90" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z90" s="9" t="n">
-        <v>0</v>
+      <c r="Z90" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA90" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB90" s="4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AC90" s="4" t="inlineStr"/>
     </row>
@@ -9889,11 +9887,11 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>28677945</v>
+        <v>6806730</v>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>SABIC Jubail Building Toastmasters Club</t>
+          <t>NISA - The Pride of Jubail Toastmasters Club</t>
         </is>
       </c>
       <c r="E91" s="5" t="n">
@@ -9911,17 +9909,17 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="J91" s="4" t="n">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="K91" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L91" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L91" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M91" s="8" t="n">
@@ -9941,7 +9939,7 @@
         <v>0</v>
       </c>
       <c r="Q91" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R91" s="9" t="n">
         <v>0</v>
@@ -9962,7 +9960,7 @@
         <v>0</v>
       </c>
       <c r="X91" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y91" s="9" t="n">
         <v>0</v>
@@ -9974,7 +9972,7 @@
         <v>1</v>
       </c>
       <c r="AB91" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC91" s="4" t="inlineStr"/>
     </row>
@@ -9986,19 +9984,19 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>3602</v>
+        <v>28677945</v>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Global Toastmasters Club</t>
+          <t>SABIC Jubail Building Toastmasters Club</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -10012,17 +10010,17 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="J92" s="4" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="K92" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L92" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L92" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M92" s="8" t="n">
@@ -10039,7 +10037,7 @@
         </is>
       </c>
       <c r="P92" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q92" s="9" t="n">
         <v>1</v>
@@ -10048,7 +10046,7 @@
         <v>0</v>
       </c>
       <c r="S92" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T92" s="9" t="n">
         <v>0</v>
@@ -10063,19 +10061,19 @@
         <v>0</v>
       </c>
       <c r="X92" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z92" s="10" t="n">
-        <v>1</v>
+      <c r="Z92" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA92" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB92" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AC92" s="4" t="inlineStr"/>
     </row>
@@ -10091,15 +10089,15 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>7645513</v>
+        <v>3602</v>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Jubail Malayalam Toastmasters Club</t>
+          <t>Global Toastmasters Club</t>
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -10113,10 +10111,10 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J93" s="4" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="K93" s="4" t="n">
         <v>0</v>
@@ -10140,16 +10138,16 @@
         </is>
       </c>
       <c r="P93" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q93" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R93" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S93" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T93" s="9" t="n">
         <v>0</v>
@@ -10164,19 +10162,19 @@
         <v>0</v>
       </c>
       <c r="X93" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z93" s="9" t="n">
-        <v>0</v>
+      <c r="Z93" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA93" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB93" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC93" s="4" t="inlineStr"/>
     </row>
@@ -10192,11 +10190,11 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>28680495</v>
+        <v>7645513</v>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>NITI Toastmasters Club</t>
+          <t>Jubail Malayalam Toastmasters Club</t>
         </is>
       </c>
       <c r="E94" s="5" t="n">
@@ -10214,17 +10212,17 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="J94" s="4" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="K94" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L94" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L94" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M94" s="8" t="n">
@@ -10265,7 +10263,7 @@
         <v>0</v>
       </c>
       <c r="X94" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y94" s="9" t="n">
         <v>0</v>
@@ -10276,7 +10274,9 @@
       <c r="AA94" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB94" s="4" t="n"/>
+      <c r="AB94" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="AC94" s="4" t="inlineStr"/>
     </row>
     <row r="95">
@@ -10291,11 +10291,11 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>28680153</v>
+        <v>28680495</v>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>SATORP Synergy</t>
+          <t>NITI Toastmasters Club</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">
@@ -10313,10 +10313,10 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J95" s="4" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="K95" s="4" t="n">
         <v>0</v>
@@ -10375,115 +10375,109 @@
       <c r="AA95" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB95" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="AB95" s="4" t="n"/>
       <c r="AC95" s="4" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>63</t>
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>1059</v>
+        <v>28680153</v>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Dhahran Toastmasters</t>
+          <t>SATORP Synergy</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G96" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I96" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="J96" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="K96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M96" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N96" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O96" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P96" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T96" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U96" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V96" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W96" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X96" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="F96" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G96" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H96" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I96" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="J96" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="K96" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="L96" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M96" s="8" t="n">
-        <v>46387</v>
-      </c>
-      <c r="N96" s="4" t="inlineStr">
-        <is>
-          <t>Officer list on time</t>
-        </is>
-      </c>
-      <c r="O96" s="7" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P96" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q96" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R96" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S96" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T96" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U96" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V96" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W96" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="X96" s="10" t="n">
-        <v>7</v>
-      </c>
       <c r="Y96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z96" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA96" s="9" t="n">
-        <v>0</v>
+      <c r="Z96" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB96" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC96" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC96" s="4" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
@@ -10497,77 +10491,77 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>4070140</v>
+        <v>1059</v>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Dhahran Women's Toastmasters Club</t>
+          <t>Dhahran Toastmasters</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F97" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G97" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H97" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I97" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="J97" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="K97" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L97" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M97" s="8" t="n">
+        <v>46387</v>
+      </c>
+      <c r="N97" s="4" t="inlineStr">
+        <is>
+          <t>Officer list on time</t>
+        </is>
+      </c>
+      <c r="O97" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P97" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q97" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T97" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U97" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F97" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G97" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H97" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I97" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="J97" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="K97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M97" s="8" t="n">
-        <v>46446</v>
-      </c>
-      <c r="N97" s="4" t="inlineStr">
-        <is>
-          <t>Officers trained Nov-Feb</t>
-        </is>
-      </c>
-      <c r="O97" s="7" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S97" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W97" s="9" t="n">
-        <v>0</v>
+      <c r="V97" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W97" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X97" s="10" t="n">
         <v>7</v>
@@ -10578,11 +10572,11 @@
       <c r="Z97" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA97" s="10" t="n">
-        <v>1</v>
+      <c r="AA97" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB97" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC97" s="4" t="inlineStr">
         <is>
@@ -10602,15 +10596,15 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>2279573</v>
+        <v>4070140</v>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>JHAH Toastmasters</t>
+          <t>Dhahran Women's Toastmasters Club</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10651,17 +10645,17 @@
         </is>
       </c>
       <c r="P98" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S98" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="Q98" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R98" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S98" s="9" t="n">
-        <v>1</v>
-      </c>
       <c r="T98" s="9" t="n">
         <v>0</v>
       </c>
@@ -10675,7 +10669,7 @@
         <v>0</v>
       </c>
       <c r="X98" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y98" s="9" t="n">
         <v>0</v>
@@ -10687,11 +10681,11 @@
         <v>1</v>
       </c>
       <c r="AB98" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AC98" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
@@ -10707,11 +10701,11 @@
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>28678325</v>
+        <v>2279573</v>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>PMU Toastmasters Club</t>
+          <t>JHAH Toastmasters</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
@@ -10729,25 +10723,25 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="J99" s="4" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L99" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L99" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M99" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N99" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O99" s="7" t="inlineStr">
@@ -10756,7 +10750,7 @@
         </is>
       </c>
       <c r="P99" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q99" s="9" t="n">
         <v>0</v>
@@ -10765,7 +10759,7 @@
         <v>0</v>
       </c>
       <c r="S99" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T99" s="9" t="n">
         <v>0</v>
@@ -10773,28 +10767,32 @@
       <c r="U99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V99" s="10" t="n">
-        <v>4</v>
+      <c r="V99" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W99" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X99" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z99" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA99" s="9" t="n">
-        <v>0</v>
+      <c r="Z99" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA99" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB99" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AC99" s="4" t="inlineStr"/>
+      <c r="AC99" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
@@ -10804,19 +10802,19 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>4772304</v>
+        <v>28678325</v>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>CS Paradigm Toastmasters Club</t>
+          <t>PMU Toastmasters Club</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10830,13 +10828,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
@@ -10844,11 +10842,11 @@
         </is>
       </c>
       <c r="M100" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N100" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O100" s="7" t="inlineStr">
@@ -10860,7 +10858,7 @@
         <v>0</v>
       </c>
       <c r="Q100" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R100" s="9" t="n">
         <v>0</v>
@@ -10874,14 +10872,14 @@
       <c r="U100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V100" s="9" t="n">
-        <v>1</v>
+      <c r="V100" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W100" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X100" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y100" s="9" t="n">
         <v>0</v>
@@ -10889,11 +10887,11 @@
       <c r="Z100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA100" s="10" t="n">
-        <v>1</v>
+      <c r="AA100" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB100" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AC100" s="4" t="inlineStr"/>
     </row>
@@ -10909,11 +10907,11 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>7225833</v>
+        <v>4772304</v>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>PM Toastmasters</t>
+          <t>CS Paradigm Toastmasters Club</t>
         </is>
       </c>
       <c r="E101" s="5" t="n">
@@ -10934,10 +10932,10 @@
         <v>8</v>
       </c>
       <c r="J101" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
@@ -10945,11 +10943,11 @@
         </is>
       </c>
       <c r="M101" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N101" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O101" s="7" t="inlineStr">
@@ -10961,7 +10959,7 @@
         <v>0</v>
       </c>
       <c r="Q101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R101" s="9" t="n">
         <v>0</v>
@@ -10976,13 +10974,13 @@
         <v>0</v>
       </c>
       <c r="V101" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W101" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X101" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y101" s="9" t="n">
         <v>0</v>
@@ -10990,8 +10988,8 @@
       <c r="Z101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA101" s="9" t="n">
-        <v>0</v>
+      <c r="AA101" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB101" s="4" t="n">
         <v>2</v>
@@ -11010,11 +11008,11 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>3616</v>
+        <v>7225833</v>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Ras Tanura Club</t>
+          <t>PM Toastmasters</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
@@ -11032,13 +11030,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J102" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
@@ -11046,11 +11044,11 @@
         </is>
       </c>
       <c r="M102" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N102" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O102" s="7" t="inlineStr">
@@ -11077,7 +11075,7 @@
         <v>0</v>
       </c>
       <c r="V102" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W102" s="9" t="n">
         <v>0</v>
@@ -11091,11 +11089,11 @@
       <c r="Z102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA102" s="10" t="n">
-        <v>1</v>
+      <c r="AA102" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB102" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AC102" s="4" t="inlineStr"/>
     </row>
@@ -11111,11 +11109,11 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>3960717</v>
+        <v>3616</v>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Vision Toastmasters Club</t>
+          <t>Ras Tanura Club</t>
         </is>
       </c>
       <c r="E103" s="5" t="n">
@@ -11133,10 +11131,10 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J103" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K103" s="4" t="n">
         <v>0</v>
@@ -11147,11 +11145,11 @@
         </is>
       </c>
       <c r="M103" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N103" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O103" s="7" t="inlineStr">
@@ -11192,11 +11190,11 @@
       <c r="Z103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA103" s="9" t="n">
-        <v>0</v>
+      <c r="AA103" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB103" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AC103" s="4" t="inlineStr"/>
     </row>
@@ -11208,19 +11206,19 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>5722</v>
+        <v>3960717</v>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Abqaiq Club</t>
+          <t>Vision Toastmasters Club</t>
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -11248,11 +11246,11 @@
         </is>
       </c>
       <c r="M104" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N104" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O104" s="7" t="inlineStr">
@@ -11290,14 +11288,14 @@
       <c r="Y104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z104" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA104" s="10" t="n">
-        <v>1</v>
+      <c r="Z104" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA104" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB104" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC104" s="4" t="inlineStr"/>
     </row>
@@ -11313,11 +11311,11 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>3222795</v>
+        <v>5722</v>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Friendly City Toastmasters Club</t>
+          <t>Abqaiq Club</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
@@ -11414,15 +11412,15 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>28678339</v>
+        <v>3222795</v>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>JHAH Alhasa Toastmasters Club</t>
+          <t>Friendly City Toastmasters Club</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -11436,76 +11434,72 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="J106" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="K106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M106" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N106" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O106" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P106" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q106" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T106" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U106" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V106" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W106" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X106" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="L106" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M106" s="8" t="n">
-        <v>46387</v>
-      </c>
-      <c r="N106" s="4" t="inlineStr">
-        <is>
-          <t>Officer list on time</t>
-        </is>
-      </c>
-      <c r="O106" s="7" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P106" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q106" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R106" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S106" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T106" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U106" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V106" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W106" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X106" s="10" t="n">
-        <v>5</v>
-      </c>
       <c r="Y106" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Z106" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA106" s="9" t="n">
-        <v>0</v>
+      <c r="AA106" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB106" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC106" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AC106" s="4" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
@@ -11519,15 +11513,15 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>7971913</v>
+        <v>28678339</v>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Saudi Arabian Drilling Academy Toastmasters</t>
+          <t>JHAH Alhasa Toastmasters Club</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>10</v>
@@ -11541,13 +11535,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J107" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L107" s="4" t="inlineStr">
         <is>
@@ -11571,7 +11565,7 @@
         <v>0</v>
       </c>
       <c r="Q107" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R107" s="9" t="n">
         <v>0</v>
@@ -11579,34 +11573,38 @@
       <c r="S107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T107" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U107" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V107" s="9" t="n">
-        <v>0</v>
+      <c r="T107" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U107" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V107" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W107" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X107" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z107" s="9" t="n">
-        <v>0</v>
+      <c r="Z107" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA107" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AB107" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC107" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AC107" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
@@ -11616,19 +11614,19 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>7643338</v>
+        <v>7971913</v>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Be Vocal Toastmasters Club</t>
+          <t>Saudi Arabian Drilling Academy Toastmasters</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11642,13 +11640,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J108" s="4" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
@@ -11656,11 +11654,11 @@
         </is>
       </c>
       <c r="M108" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N108" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O108" s="7" t="inlineStr">
@@ -11686,11 +11684,11 @@
       <c r="U108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V108" s="10" t="n">
-        <v>4</v>
+      <c r="V108" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W108" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X108" s="10" t="n">
         <v>6</v>
@@ -11698,20 +11696,16 @@
       <c r="Y108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z108" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA108" s="10" t="n">
-        <v>1</v>
+      <c r="Z108" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA108" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB108" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC108" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AC108" s="4" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -11725,15 +11719,15 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>28675720</v>
+        <v>7643338</v>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>KBR-AMCDE Toastmasters</t>
+          <t>Be Vocal Toastmasters Club</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11747,13 +11741,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J109" s="4" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
@@ -11791,14 +11785,14 @@
       <c r="U109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V109" s="9" t="n">
-        <v>0</v>
+      <c r="V109" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W109" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X109" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y109" s="9" t="n">
         <v>0</v>
@@ -11810,9 +11804,13 @@
         <v>1</v>
       </c>
       <c r="AB109" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC109" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC109" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
@@ -11826,15 +11824,15 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>1014368</v>
+        <v>28675720</v>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Professional Speakers</t>
+          <t>KBR-AMCDE Toastmasters</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -11848,25 +11846,25 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J110" s="4" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="K110" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L110" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L110" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M110" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N110" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O110" s="7" t="inlineStr">
@@ -11899,7 +11897,7 @@
         <v>0</v>
       </c>
       <c r="X110" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y110" s="9" t="n">
         <v>0</v>
@@ -11907,35 +11905,31 @@
       <c r="Z110" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA110" s="9" t="n">
-        <v>0</v>
+      <c r="AA110" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB110" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC110" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="AC110" s="4" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>657697</v>
+        <v>1014368</v>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Indian Engineers Toastmasters Club</t>
+          <t>Professional Speakers</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
@@ -11953,10 +11947,10 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J111" s="4" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="K111" s="4" t="n">
         <v>0</v>
@@ -11967,11 +11961,11 @@
         </is>
       </c>
       <c r="M111" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N111" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O111" s="7" t="inlineStr">
@@ -12004,21 +11998,25 @@
         <v>0</v>
       </c>
       <c r="X111" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z111" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA111" s="10" t="n">
-        <v>1</v>
+      <c r="Z111" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA111" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB111" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC111" s="4" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="AC111" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
@@ -12032,11 +12030,11 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>4819591</v>
+        <v>657697</v>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>McDermott KSA</t>
+          <t>Indian Engineers Toastmasters Club</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
@@ -12054,10 +12052,10 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J112" s="4" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="K112" s="4" t="n">
         <v>0</v>
@@ -12133,15 +12131,15 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>586780</v>
+        <v>4819591</v>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Sahara Toastmasters Club</t>
+          <t>McDermott KSA</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -12155,10 +12153,10 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J113" s="4" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="K113" s="4" t="n">
         <v>0</v>
@@ -12193,11 +12191,11 @@
       <c r="S113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T113" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U113" s="10" t="n">
-        <v>1</v>
+      <c r="T113" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U113" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V113" s="9" t="n">
         <v>0</v>
@@ -12206,7 +12204,7 @@
         <v>0</v>
       </c>
       <c r="X113" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y113" s="9" t="n">
         <v>0</v>
@@ -12234,15 +12232,15 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>2382680</v>
+        <v>586780</v>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Seaview Toastmasters Club</t>
+          <t>Sahara Toastmasters Club</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -12270,11 +12268,11 @@
         </is>
       </c>
       <c r="M114" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N114" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O114" s="7" t="inlineStr">
@@ -12294,11 +12292,11 @@
       <c r="S114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T114" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U114" s="9" t="n">
-        <v>0</v>
+      <c r="T114" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U114" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V114" s="9" t="n">
         <v>0</v>
@@ -12315,11 +12313,11 @@
       <c r="Z114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA114" s="9" t="n">
-        <v>0</v>
+      <c r="AA114" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB114" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC114" s="4" t="inlineStr"/>
     </row>
@@ -12331,19 +12329,19 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>09</t>
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>3728020</v>
+        <v>2382680</v>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Alturki Toastmasters Club</t>
+          <t>Seaview Toastmasters Club</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -12357,70 +12355,70 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K115" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M115" s="8" t="n">
+        <v>46387</v>
+      </c>
+      <c r="N115" s="4" t="inlineStr">
+        <is>
+          <t>Officer list on time</t>
+        </is>
+      </c>
+      <c r="O115" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P115" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R115" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T115" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U115" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V115" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W115" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X115" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="L115" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M115" s="8" t="n">
-        <v>46446</v>
-      </c>
-      <c r="N115" s="4" t="inlineStr">
-        <is>
-          <t>Officers trained Nov-Feb</t>
-        </is>
-      </c>
-      <c r="O115" s="7" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P115" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q115" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R115" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S115" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T115" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U115" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V115" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W115" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X115" s="10" t="n">
-        <v>7</v>
-      </c>
       <c r="Y115" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Z115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA115" s="10" t="n">
-        <v>1</v>
+      <c r="AA115" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB115" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AC115" s="4" t="inlineStr"/>
     </row>
@@ -12436,11 +12434,11 @@
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>28679019</v>
+        <v>3728020</v>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Level Up Advance Toastmasters Club</t>
+          <t>Alturki Toastmasters Club</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
@@ -12458,17 +12456,17 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L116" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L116" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M116" s="8" t="n">
@@ -12499,29 +12497,29 @@
       <c r="T116" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U116" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V116" s="9" t="n">
-        <v>0</v>
+      <c r="U116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V116" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W116" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X116" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA116" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB116" s="4" t="n">
         <v>6</v>
-      </c>
-      <c r="Y116" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z116" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA116" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB116" s="4" t="n">
-        <v>3</v>
       </c>
       <c r="AC116" s="4" t="inlineStr"/>
     </row>
@@ -12537,15 +12535,15 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>8258</v>
+        <v>28679019</v>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Oasis Toastmasters Club</t>
+          <t>Level Up Advance Toastmasters Club</t>
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12597,11 +12595,11 @@
       <c r="S117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T117" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U117" s="9" t="n">
-        <v>0</v>
+      <c r="T117" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U117" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V117" s="9" t="n">
         <v>0</v>
@@ -12622,7 +12620,7 @@
         <v>1</v>
       </c>
       <c r="AB117" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC117" s="4" t="inlineStr"/>
     </row>
@@ -12638,11 +12636,11 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>5680734</v>
+        <v>8258</v>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Sparkle Toastmasters Club</t>
+          <t>Oasis Toastmasters Club</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
@@ -12723,7 +12721,7 @@
         <v>1</v>
       </c>
       <c r="AB118" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC118" s="4" t="inlineStr"/>
     </row>
@@ -12735,15 +12733,15 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>28677051</v>
+        <v>5680734</v>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Almajdouie Toastmasters Club</t>
+          <t>Sparkle Toastmasters Club</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
@@ -12824,7 +12822,7 @@
         <v>1</v>
       </c>
       <c r="AB119" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC119" s="4" t="inlineStr"/>
     </row>
@@ -12840,15 +12838,15 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>990731</v>
+        <v>28677051</v>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Diamond Toastmasters Club</t>
+          <t>Almajdouie Toastmasters Club</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -12862,17 +12860,17 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J120" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L120" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L120" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M120" s="8" t="n">
@@ -12906,14 +12904,14 @@
       <c r="U120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V120" s="10" t="n">
-        <v>4</v>
+      <c r="V120" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W120" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X120" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y120" s="9" t="n">
         <v>0</v>
@@ -12925,7 +12923,7 @@
         <v>1</v>
       </c>
       <c r="AB120" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC120" s="4" t="inlineStr"/>
     </row>
@@ -12941,11 +12939,11 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>7299183</v>
+        <v>990731</v>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Pakistani Community Toastmasters Club</t>
+          <t>Diamond Toastmasters Club</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
@@ -12963,17 +12961,17 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J121" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L121" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L121" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M121" s="8" t="n">
@@ -13001,20 +12999,20 @@
       <c r="S121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T121" s="10" t="n">
-        <v>1</v>
+      <c r="T121" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V121" s="9" t="n">
-        <v>0</v>
+      <c r="V121" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W121" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X121" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y121" s="9" t="n">
         <v>0</v>
@@ -13042,15 +13040,15 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>1340602</v>
+        <v>7299183</v>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>WORLEY TOASTMASTERS CLUB</t>
+          <t>Pakistani Community Toastmasters Club</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -13102,8 +13100,8 @@
       <c r="S122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T122" s="9" t="n">
-        <v>0</v>
+      <c r="T122" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U122" s="9" t="n">
         <v>0</v>
@@ -13115,7 +13113,7 @@
         <v>0</v>
       </c>
       <c r="X122" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y122" s="9" t="n">
         <v>0</v>
@@ -13139,15 +13137,15 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>51</t>
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>6800081</v>
+        <v>1340602</v>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Eloquent Speakers Toastmasters Club</t>
+          <t>WORLEY TOASTMASTERS CLUB</t>
         </is>
       </c>
       <c r="E123" s="5" t="n">
@@ -13165,10 +13163,10 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J123" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K123" s="4" t="n">
         <v>0</v>
@@ -13228,7 +13226,7 @@
         <v>1</v>
       </c>
       <c r="AB123" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AC123" s="4" t="inlineStr"/>
     </row>
@@ -13244,15 +13242,15 @@
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>4251144</v>
+        <v>6800081</v>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Pakistan Engineers Toastmaster Club</t>
+          <t>Eloquent Speakers Toastmasters Club</t>
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -13266,10 +13264,10 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J124" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K124" s="4" t="n">
         <v>0</v>
@@ -13304,8 +13302,8 @@
       <c r="S124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T124" s="10" t="n">
-        <v>1</v>
+      <c r="T124" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U124" s="9" t="n">
         <v>0</v>
@@ -13329,7 +13327,7 @@
         <v>1</v>
       </c>
       <c r="AB124" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC124" s="4" t="inlineStr"/>
     </row>
@@ -13345,15 +13343,15 @@
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>3528237</v>
+        <v>4251144</v>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Prudent Family Toastmasters</t>
+          <t>Pakistan Engineers Toastmaster Club</t>
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -13367,10 +13365,10 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J125" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K125" s="4" t="n">
         <v>0</v>
@@ -13405,8 +13403,8 @@
       <c r="S125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T125" s="9" t="n">
-        <v>0</v>
+      <c r="T125" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U125" s="9" t="n">
         <v>0</v>
@@ -13418,7 +13416,7 @@
         <v>0</v>
       </c>
       <c r="X125" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y125" s="9" t="n">
         <v>0</v>
@@ -13430,7 +13428,7 @@
         <v>1</v>
       </c>
       <c r="AB125" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AC125" s="4" t="inlineStr"/>
     </row>
@@ -13446,11 +13444,11 @@
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>2175364</v>
+        <v>3528237</v>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>TAPROBANE Toastmasters Club</t>
+          <t>Prudent Family Toastmasters</t>
         </is>
       </c>
       <c r="E126" s="5" t="n">
@@ -13468,10 +13466,10 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J126" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K126" s="4" t="n">
         <v>0</v>
@@ -13482,11 +13480,11 @@
         </is>
       </c>
       <c r="M126" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N126" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O126" s="7" t="inlineStr">
@@ -13519,7 +13517,7 @@
         <v>0</v>
       </c>
       <c r="X126" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y126" s="9" t="n">
         <v>0</v>
@@ -13527,35 +13525,35 @@
       <c r="Z126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA126" s="9" t="n">
-        <v>0</v>
+      <c r="AA126" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB126" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AC126" s="4" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>52</t>
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>5975201</v>
+        <v>2175364</v>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Al-Zulfi Toastmasters Women's Club</t>
+          <t>TAPROBANE Toastmasters Club</t>
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>10</v>
@@ -13569,13 +13567,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J127" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
@@ -13583,11 +13581,11 @@
         </is>
       </c>
       <c r="M127" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N127" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O127" s="7" t="inlineStr">
@@ -13595,11 +13593,11 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P127" s="10" t="n">
-        <v>4</v>
+      <c r="P127" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Q127" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R127" s="9" t="n">
         <v>0</v>
@@ -13607,14 +13605,14 @@
       <c r="S127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T127" s="10" t="n">
-        <v>1</v>
+      <c r="T127" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U127" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V127" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W127" s="9" t="n">
         <v>0</v>
@@ -13628,11 +13626,11 @@
       <c r="Z127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA127" s="10" t="n">
-        <v>1</v>
+      <c r="AA127" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB127" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC127" s="4" t="inlineStr"/>
     </row>
@@ -13648,15 +13646,15 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>28678830</v>
+        <v>5975201</v>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Bussma Toastmasters Club</t>
+          <t>Al-Zulfi Toastmasters Women's Club</t>
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13670,17 +13668,17 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="J128" s="4" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="L128" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L128" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M128" s="8" t="n">
@@ -13697,43 +13695,43 @@
         </is>
       </c>
       <c r="P128" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q128" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q128" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R128" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T128" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U128" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V128" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="R128" s="10" t="n">
+      <c r="W128" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X128" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y128" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z128" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA128" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB128" s="4" t="n">
         <v>3</v>
-      </c>
-      <c r="S128" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T128" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U128" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V128" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W128" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="X128" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y128" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z128" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA128" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB128" s="4" t="n">
-        <v>10</v>
       </c>
       <c r="AC128" s="4" t="inlineStr"/>
     </row>
@@ -13749,15 +13747,15 @@
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>28680701</v>
+        <v>28678830</v>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Red Crescent Authority Toastmasters Club</t>
+          <t>Bussma Toastmasters Club</t>
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13771,13 +13769,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="J129" s="4" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L129" s="4" t="inlineStr">
         <is>
@@ -13797,32 +13795,32 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W129" s="9" t="n">
-        <v>0</v>
+      <c r="P129" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q129" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R129" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="S129" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T129" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U129" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V129" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W129" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="X129" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y129" s="9" t="n">
         <v>0</v>
@@ -13833,7 +13831,9 @@
       <c r="AA129" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB129" s="4" t="n"/>
+      <c r="AB129" s="4" t="n">
+        <v>10</v>
+      </c>
       <c r="AC129" s="4" t="inlineStr"/>
     </row>
     <row r="130">
@@ -13848,15 +13848,15 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>5413205</v>
+        <v>28680701</v>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>STC Riyadh</t>
+          <t>Red Crescent Authority Toastmasters Club</t>
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>10</v>
@@ -13870,17 +13870,17 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="J130" s="4" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="K130" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L130" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L130" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M130" s="8" t="n">
@@ -13920,21 +13920,19 @@
       <c r="W130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X130" s="9" t="n">
-        <v>1</v>
+      <c r="X130" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z130" s="9" t="n">
-        <v>0</v>
+      <c r="Z130" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA130" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB130" s="4" t="n">
-        <v>2</v>
-      </c>
+      <c r="AB130" s="4" t="n"/>
       <c r="AC130" s="4" t="inlineStr"/>
     </row>
     <row r="131">
@@ -13949,15 +13947,15 @@
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>28677980</v>
+        <v>5413205</v>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>The Inspiring Club</t>
+          <t>STC Riyadh</t>
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>10</v>
@@ -13971,17 +13969,17 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="J131" s="4" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="L131" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L131" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M131" s="8" t="n">
@@ -13998,49 +13996,45 @@
         </is>
       </c>
       <c r="P131" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q131" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q131" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R131" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S131" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T131" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U131" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V131" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W131" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X131" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y131" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z131" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA131" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB131" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="R131" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S131" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T131" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U131" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V131" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W131" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="X131" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y131" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z131" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA131" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB131" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC131" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+      <c r="AC131" s="4" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
@@ -14054,15 +14048,15 @@
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>1597596</v>
+        <v>28677980</v>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>Yallah Banat Ariyadh Toastmasters Club</t>
+          <t>The Inspiring Club</t>
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>10</v>
@@ -14076,17 +14070,17 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="J132" s="4" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L132" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>15</v>
+      </c>
+      <c r="L132" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M132" s="8" t="n">
@@ -14103,10 +14097,10 @@
         </is>
       </c>
       <c r="P132" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q132" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="Q132" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R132" s="9" t="n">
         <v>0</v>
@@ -14114,34 +14108,38 @@
       <c r="S132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T132" s="9" t="n">
-        <v>0</v>
+      <c r="T132" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V132" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W132" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X132" s="9" t="n">
-        <v>1</v>
+      <c r="V132" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W132" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="X132" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z132" s="9" t="n">
-        <v>0</v>
+      <c r="Z132" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA132" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB132" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC132" s="4" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="AC132" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
@@ -14151,19 +14149,19 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>28676781</v>
+        <v>1597596</v>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Al Rou'ya Club</t>
+          <t>Yallah Banat Ariyadh Toastmasters Club</t>
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -14177,17 +14175,17 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="J133" s="4" t="n">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="L133" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L133" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M133" s="8" t="n">
@@ -14203,11 +14201,11 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P133" s="10" t="n">
-        <v>5</v>
+      <c r="P133" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Q133" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R133" s="9" t="n">
         <v>0</v>
@@ -14221,26 +14219,26 @@
       <c r="U133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V133" s="10" t="n">
+      <c r="V133" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W133" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X133" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y133" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z133" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA133" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB133" s="4" t="n">
         <v>4</v>
-      </c>
-      <c r="W133" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X133" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y133" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z133" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA133" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB133" s="4" t="n">
-        <v>10</v>
       </c>
       <c r="AC133" s="4" t="inlineStr"/>
     </row>
@@ -14256,15 +14254,15 @@
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>28677871</v>
+        <v>28676781</v>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Industrial &amp; Mining Organization Toastmasters Club</t>
+          <t>Al Rou'ya Club</t>
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>10</v>
@@ -14278,25 +14276,25 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="J134" s="4" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L134" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>13</v>
+      </c>
+      <c r="L134" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M134" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N134" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O134" s="7" t="inlineStr">
@@ -14304,11 +14302,11 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P134" s="9" t="n">
-        <v>0</v>
+      <c r="P134" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Q134" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R134" s="9" t="n">
         <v>0</v>
@@ -14322,11 +14320,11 @@
       <c r="U134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V134" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W134" s="9" t="n">
-        <v>0</v>
+      <c r="V134" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W134" s="10" t="n">
+        <v>9</v>
       </c>
       <c r="X134" s="10" t="n">
         <v>4</v>
@@ -14334,14 +14332,14 @@
       <c r="Y134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z134" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA134" s="9" t="n">
-        <v>0</v>
+      <c r="Z134" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA134" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB134" s="4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AC134" s="4" t="inlineStr"/>
     </row>
@@ -14357,15 +14355,15 @@
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>28678889</v>
+        <v>28677871</v>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Majmaah University Toastmasters</t>
+          <t>Industrial &amp; Mining Organization Toastmasters Club</t>
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -14379,13 +14377,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J135" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L135" s="7" t="inlineStr">
         <is>
@@ -14393,11 +14391,11 @@
         </is>
       </c>
       <c r="M135" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N135" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O135" s="7" t="inlineStr">
@@ -14405,41 +14403,41 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P135" s="10" t="n">
+      <c r="P135" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R135" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T135" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U135" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V135" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W135" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X135" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="Q135" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R135" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S135" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T135" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U135" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V135" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W135" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X135" s="10" t="n">
-        <v>5</v>
-      </c>
       <c r="Y135" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Z135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA135" s="10" t="n">
-        <v>1</v>
+      <c r="AA135" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB135" s="4" t="n">
         <v>1</v>
@@ -14458,15 +14456,15 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>1536532</v>
+        <v>28678889</v>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>The Gold Toastmasters Club (arabic / Men)</t>
+          <t>Majmaah University Toastmasters</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -14480,17 +14478,17 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="J136" s="4" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="L136" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L136" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M136" s="8" t="n">
@@ -14506,17 +14504,17 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P136" s="9" t="n">
-        <v>0</v>
+      <c r="P136" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q136" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R136" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S136" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T136" s="9" t="n">
         <v>0</v>
@@ -14524,32 +14522,28 @@
       <c r="U136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V136" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W136" s="10" t="n">
-        <v>12</v>
+      <c r="V136" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W136" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X136" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z136" s="10" t="n">
-        <v>1</v>
+      <c r="Z136" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA136" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB136" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC136" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC136" s="4" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
@@ -14559,19 +14553,19 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>28676557</v>
+        <v>1536532</v>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Al-Kharj Toastmasters</t>
+          <t>The Gold Toastmasters Club (arabic / Men)</t>
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F137" s="6" t="n">
         <v>10</v>
@@ -14585,17 +14579,17 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="J137" s="4" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L137" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>16</v>
+      </c>
+      <c r="L137" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M137" s="8" t="n">
@@ -14615,13 +14609,13 @@
         <v>0</v>
       </c>
       <c r="Q137" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R137" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S137" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T137" s="9" t="n">
         <v>0</v>
@@ -14629,11 +14623,11 @@
       <c r="U137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V137" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W137" s="9" t="n">
-        <v>0</v>
+      <c r="V137" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W137" s="10" t="n">
+        <v>12</v>
       </c>
       <c r="X137" s="10" t="n">
         <v>4</v>
@@ -14641,16 +14635,20 @@
       <c r="Y137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z137" s="9" t="n">
-        <v>0</v>
+      <c r="Z137" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA137" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB137" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC137" s="4" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="AC137" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
@@ -14664,15 +14662,15 @@
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>28680095</v>
+        <v>28676557</v>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>Albayan Toastmasters Club</t>
+          <t>Al-Kharj Toastmasters</t>
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14686,17 +14684,17 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="J138" s="4" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="L138" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L138" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M138" s="8" t="n">
@@ -14730,15 +14728,15 @@
       <c r="U138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V138" s="10" t="n">
+      <c r="V138" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W138" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X138" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W138" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="X138" s="10" t="n">
-        <v>5</v>
-      </c>
       <c r="Y138" s="9" t="n">
         <v>0</v>
       </c>
@@ -14749,7 +14747,7 @@
         <v>1</v>
       </c>
       <c r="AB138" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AC138" s="4" t="inlineStr"/>
     </row>
@@ -14765,15 +14763,15 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>5272586</v>
+        <v>28680095</v>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Alrowad</t>
+          <t>Albayan Toastmasters Club</t>
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F139" s="6" t="n">
         <v>10</v>
@@ -14787,13 +14785,13 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="J139" s="4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L139" s="4" t="inlineStr">
         <is>
@@ -14814,7 +14812,7 @@
         </is>
       </c>
       <c r="P139" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q139" s="9" t="n">
         <v>0</v>
@@ -14822,8 +14820,8 @@
       <c r="R139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S139" s="10" t="n">
-        <v>2</v>
+      <c r="S139" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="T139" s="9" t="n">
         <v>0</v>
@@ -14834,29 +14832,25 @@
       <c r="V139" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W139" s="9" t="n">
-        <v>0</v>
+      <c r="W139" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X139" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z139" s="10" t="n">
-        <v>1</v>
+      <c r="Z139" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA139" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB139" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC139" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC139" s="4" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
@@ -14870,11 +14864,11 @@
         </is>
       </c>
       <c r="C140" s="4" t="n">
-        <v>5430717</v>
+        <v>5272586</v>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>Alsafwah Toastmasters Club</t>
+          <t>Alrowad</t>
         </is>
       </c>
       <c r="E140" s="5" t="n">
@@ -14892,13 +14886,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="J140" s="4" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L140" s="4" t="inlineStr">
         <is>
@@ -14919,16 +14913,16 @@
         </is>
       </c>
       <c r="P140" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q140" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R140" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S140" s="10" t="n">
         <v>2</v>
-      </c>
-      <c r="Q140" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R140" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S140" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="T140" s="9" t="n">
         <v>0</v>
@@ -14939,8 +14933,8 @@
       <c r="V140" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W140" s="10" t="n">
-        <v>6</v>
+      <c r="W140" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X140" s="10" t="n">
         <v>4</v>
@@ -14955,9 +14949,13 @@
         <v>1</v>
       </c>
       <c r="AB140" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC140" s="4" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="AC140" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
@@ -14971,15 +14969,15 @@
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>6133205</v>
+        <v>5430717</v>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Riyadh Leaders</t>
+          <t>Alsafwah Toastmasters Club</t>
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F141" s="6" t="n">
         <v>10</v>
@@ -14993,13 +14991,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="J141" s="4" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L141" s="4" t="inlineStr">
         <is>
@@ -15019,32 +15017,32 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P141" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q141" s="10" t="n">
+      <c r="P141" s="9" t="n">
         <v>2</v>
       </c>
+      <c r="Q141" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="R141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S141" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T141" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U141" s="10" t="n">
-        <v>2</v>
+      <c r="S141" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T141" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U141" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V141" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W141" s="9" t="n">
-        <v>3</v>
+      <c r="W141" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X141" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y141" s="9" t="n">
         <v>0</v>
@@ -15068,19 +15066,19 @@
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>4725065</v>
+        <v>6133205</v>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>Al-Qassim</t>
+          <t>Riyadh Leaders</t>
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F142" s="6" t="n">
         <v>10</v>
@@ -15094,13 +15092,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="J142" s="4" t="n">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
@@ -15120,44 +15118,44 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P142" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q142" s="9" t="n">
-        <v>0</v>
+      <c r="P142" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q142" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S142" s="9" t="n">
-        <v>0</v>
+      <c r="S142" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T142" s="10" t="n">
         <v>1</v>
       </c>
       <c r="U142" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V142" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W142" s="10" t="n">
-        <v>5</v>
+      <c r="W142" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="X142" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z142" s="9" t="n">
-        <v>0</v>
+      <c r="Z142" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA142" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB142" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC142" s="4" t="inlineStr"/>
     </row>
@@ -15173,15 +15171,15 @@
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>28677311</v>
+        <v>4725065</v>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Multaqa Almubdieen</t>
+          <t>Al-Qassim</t>
         </is>
       </c>
       <c r="E143" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F143" s="6" t="n">
         <v>10</v>
@@ -15195,13 +15193,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J143" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L143" s="4" t="inlineStr">
         <is>
@@ -15236,17 +15234,17 @@
       <c r="T143" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U143" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V143" s="9" t="n">
+      <c r="U143" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="W143" s="9" t="n">
-        <v>0</v>
+      <c r="V143" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W143" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X143" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y143" s="9" t="n">
         <v>0</v>
@@ -15258,7 +15256,7 @@
         <v>1</v>
       </c>
       <c r="AB143" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC143" s="4" t="inlineStr"/>
     </row>
@@ -15274,15 +15272,15 @@
         </is>
       </c>
       <c r="C144" s="4" t="n">
-        <v>6911216</v>
+        <v>28677311</v>
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>Sulaiman Al Rajhi College Male Students</t>
+          <t>Multaqa Almubdieen</t>
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F144" s="6" t="n">
         <v>10</v>
@@ -15296,17 +15294,17 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="J144" s="4" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L144" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>3</v>
+      </c>
+      <c r="L144" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M144" s="8" t="n">
@@ -15334,20 +15332,20 @@
       <c r="S144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T144" s="9" t="n">
-        <v>0</v>
+      <c r="T144" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U144" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V144" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W144" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X144" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y144" s="9" t="n">
         <v>0</v>
@@ -15359,7 +15357,7 @@
         <v>1</v>
       </c>
       <c r="AB144" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC144" s="4" t="inlineStr"/>
     </row>
@@ -15375,15 +15373,15 @@
         </is>
       </c>
       <c r="C145" s="4" t="n">
-        <v>28675387</v>
+        <v>6911216</v>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>Unayza TMC</t>
+          <t>Sulaiman Al Rajhi College Male Students</t>
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F145" s="6" t="n">
         <v>10</v>
@@ -15397,10 +15395,10 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J145" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K145" s="4" t="n">
         <v>0</v>
@@ -15426,46 +15424,147 @@
       <c r="P145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q145" s="10" t="n">
+      <c r="Q145" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R145" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S145" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T145" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U145" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V145" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W145" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X145" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y145" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z145" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA145" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB145" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC145" s="4" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="B146" s="4" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="C146" s="4" t="n">
+        <v>28675387</v>
+      </c>
+      <c r="D146" s="4" t="inlineStr">
+        <is>
+          <t>Unayza TMC</t>
+        </is>
+      </c>
+      <c r="E146" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F146" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G146" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H146" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I146" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="J146" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="K146" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L146" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M146" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N146" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O146" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P146" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q146" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R145" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S145" s="10" t="n">
+      <c r="R146" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S146" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="T145" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U145" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V145" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W145" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X145" s="10" t="n">
+      <c r="T146" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U146" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V146" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W146" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X146" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="Y145" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z145" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA145" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB145" s="4" t="n">
+      <c r="Y146" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z146" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA146" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB146" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AC145" s="4" t="inlineStr"/>
+      <c r="AC146" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC145"/>
+  <autoFilter ref="A1:AC146"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15747,25 +15846,25 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
         <v>4</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>4</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="9">

--- a/docs/d/79/inyear.xlsx
+++ b/docs/d/79/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,11 @@
       <c r="AB3" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC3" s="4" t="inlineStr"/>
+      <c r="AC3" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -1230,7 +1234,11 @@
       <c r="AB5" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC5" s="4" t="inlineStr"/>
+      <c r="AC5" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -1642,7 +1650,11 @@
       <c r="AB9" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC9" s="4" t="inlineStr"/>
+      <c r="AC9" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1743,7 +1755,11 @@
       <c r="AB10" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC10" s="4" t="inlineStr"/>
+      <c r="AC10" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1844,7 +1860,11 @@
       <c r="AB11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC11" s="4" t="inlineStr"/>
+      <c r="AC11" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -2454,7 +2474,11 @@
       <c r="AB17" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC17" s="4" t="inlineStr"/>
+      <c r="AC17" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -2862,7 +2886,11 @@
       <c r="AB21" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC21" s="4" t="inlineStr"/>
+      <c r="AC21" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -3371,7 +3399,11 @@
       <c r="AB26" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC26" s="4" t="inlineStr"/>
+      <c r="AC26" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -4395,7 +4427,11 @@
       <c r="AB36" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC36" s="4" t="inlineStr"/>
+      <c r="AC36" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -6427,7 +6463,11 @@
       <c r="AB56" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC56" s="4" t="inlineStr"/>
+      <c r="AC56" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -7138,7 +7178,11 @@
       <c r="AB63" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC63" s="4" t="inlineStr"/>
+      <c r="AC63" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -9873,7 +9917,11 @@
       <c r="AB90" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC90" s="4" t="inlineStr"/>
+      <c r="AC90" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -11911,7 +11959,11 @@
       <c r="AB110" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC110" s="4" t="inlineStr"/>
+      <c r="AC110" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -13834,7 +13886,11 @@
       <c r="AB129" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC129" s="4" t="inlineStr"/>
+      <c r="AC129" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
@@ -14341,7 +14397,11 @@
       <c r="AB134" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC134" s="4" t="inlineStr"/>
+      <c r="AC134" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
@@ -15056,7 +15116,11 @@
       <c r="AB141" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC141" s="4" t="inlineStr"/>
+      <c r="AC141" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
@@ -15157,7 +15221,11 @@
       <c r="AB142" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC142" s="4" t="inlineStr"/>
+      <c r="AC142" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
@@ -15359,7 +15427,11 @@
       <c r="AB144" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC144" s="4" t="inlineStr"/>
+      <c r="AC144" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">

--- a/docs/d/79/inyear.xlsx
+++ b/docs/d/79/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 27 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 27 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 105 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 104 clubs short</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
         <v>1</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" s="9" t="n">
         <v>0</v>
@@ -2193,7 +2193,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2207,13 +2207,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-11</v>
+        <v>-5</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
@@ -2251,11 +2251,11 @@
       <c r="U15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V15" s="9" t="n">
-        <v>0</v>
+      <c r="V15" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W15" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X15" s="10" t="n">
         <v>7</v>
@@ -5770,7 +5770,7 @@
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>10</v>
@@ -5813,8 +5813,8 @@
       <c r="P50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" s="9" t="n">
-        <v>1</v>
+      <c r="Q50" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R50" s="9" t="n">
         <v>0</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -7357,8 +7357,8 @@
       <c r="S65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T65" s="9" t="n">
-        <v>0</v>
+      <c r="T65" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U65" s="9" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>10</v>
@@ -7476,8 +7476,8 @@
       <c r="Y66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z66" s="9" t="n">
-        <v>0</v>
+      <c r="Z66" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA66" s="10" t="n">
         <v>1</v>
@@ -15610,7 +15610,7 @@
         <v>1</v>
       </c>
       <c r="U146" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V146" s="9" t="n">
         <v>0</v>
@@ -15822,7 +15822,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -16053,7 +16053,7 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -16152,7 +16152,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -16185,7 +16185,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>

--- a/docs/d/79/inyear.xlsx
+++ b/docs/d/79/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 27 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 27 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 104 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 71 clubs short</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>10</v>
@@ -1019,8 +1019,8 @@
       <c r="Y3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z3" s="9" t="n">
-        <v>0</v>
+      <c r="Z3" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA3" s="10" t="n">
         <v>1</v>
@@ -1054,7 +1054,7 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>10</v>
@@ -1124,8 +1124,8 @@
       <c r="Y4" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z4" s="9" t="n">
-        <v>0</v>
+      <c r="Z4" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA4" s="10" t="n">
         <v>1</v>
@@ -1466,7 +1466,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>10</v>
@@ -1536,8 +1536,8 @@
       <c r="Y8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z8" s="9" t="n">
-        <v>0</v>
+      <c r="Z8" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA8" s="10" t="n">
         <v>1</v>
@@ -1676,7 +1676,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1746,8 +1746,8 @@
       <c r="Y10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z10" s="9" t="n">
-        <v>0</v>
+      <c r="Z10" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA10" s="10" t="n">
         <v>1</v>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1851,8 +1851,8 @@
       <c r="Y11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z11" s="9" t="n">
-        <v>0</v>
+      <c r="Z11" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA11" s="10" t="n">
         <v>1</v>
@@ -1886,7 +1886,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>10</v>
@@ -1900,17 +1900,17 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M12" s="8" t="n">
@@ -1945,7 +1945,7 @@
         <v>0</v>
       </c>
       <c r="V12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W12" s="9" t="n">
         <v>0</v>
@@ -1956,8 +1956,8 @@
       <c r="Y12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z12" s="9" t="n">
-        <v>0</v>
+      <c r="Z12" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA12" s="10" t="n">
         <v>1</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -2057,8 +2057,8 @@
       <c r="Y13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z13" s="9" t="n">
-        <v>0</v>
+      <c r="Z13" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA13" s="10" t="n">
         <v>1</v>
@@ -2294,7 +2294,7 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>10</v>
@@ -2364,8 +2364,8 @@
       <c r="Y16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z16" s="9" t="n">
-        <v>0</v>
+      <c r="Z16" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA16" s="10" t="n">
         <v>1</v>
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2552,8 +2552,8 @@
       <c r="S18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T18" s="9" t="n">
-        <v>0</v>
+      <c r="T18" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U18" s="9" t="n">
         <v>0</v>
@@ -2702,7 +2702,7 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>10</v>
@@ -2772,8 +2772,8 @@
       <c r="Y20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z20" s="9" t="n">
-        <v>0</v>
+      <c r="Z20" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA20" s="10" t="n">
         <v>1</v>
@@ -2976,8 +2976,8 @@
       <c r="W22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X22" s="9" t="n">
-        <v>1</v>
+      <c r="X22" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y22" s="9" t="n">
         <v>0</v>
@@ -3178,8 +3178,8 @@
       <c r="W24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X24" s="9" t="n">
-        <v>2</v>
+      <c r="X24" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y24" s="9" t="n">
         <v>0</v>
@@ -3320,7 +3320,7 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>10</v>
@@ -3363,8 +3363,8 @@
       <c r="P26" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="Q26" s="9" t="n">
-        <v>1</v>
+      <c r="Q26" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R26" s="9" t="n">
         <v>0</v>
@@ -3425,7 +3425,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3465,8 +3465,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P27" s="9" t="n">
-        <v>3</v>
+      <c r="P27" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q27" s="9" t="n">
         <v>0</v>
@@ -3635,7 +3635,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3705,8 +3705,8 @@
       <c r="Y29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z29" s="9" t="n">
-        <v>0</v>
+      <c r="Z29" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA29" s="10" t="n">
         <v>1</v>
@@ -3804,8 +3804,8 @@
       <c r="W30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X30" s="9" t="n">
-        <v>0</v>
+      <c r="X30" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y30" s="9" t="n">
         <v>0</v>
@@ -3814,7 +3814,7 @@
         <v>0</v>
       </c>
       <c r="AA30" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB30" s="4" t="n"/>
       <c r="AC30" s="4" t="inlineStr"/>
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F32" s="6" t="n">
         <v>10</v>
@@ -3954,13 +3954,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>1</v>
       </c>
       <c r="Q32" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" s="9" t="n">
         <v>0</v>
@@ -3992,14 +3992,14 @@
       <c r="S32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T32" s="9" t="n">
-        <v>0</v>
+      <c r="T32" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V32" s="9" t="n">
-        <v>3</v>
+      <c r="V32" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W32" s="9" t="n">
         <v>0</v>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>10</v>
@@ -4081,8 +4081,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P33" s="9" t="n">
-        <v>3</v>
+      <c r="P33" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q33" s="10" t="n">
         <v>2</v>
@@ -4146,7 +4146,7 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>10</v>
@@ -4216,8 +4216,8 @@
       <c r="Y34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z34" s="9" t="n">
-        <v>0</v>
+      <c r="Z34" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA34" s="10" t="n">
         <v>1</v>
@@ -4972,13 +4972,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>4</v>
       </c>
       <c r="W42" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X42" s="10" t="n">
         <v>4</v>
@@ -5063,7 +5063,7 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>10</v>
@@ -5133,8 +5133,8 @@
       <c r="Y43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z43" s="9" t="n">
-        <v>0</v>
+      <c r="Z43" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA43" s="10" t="n">
         <v>1</v>
@@ -5265,7 +5265,7 @@
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5335,8 +5335,8 @@
       <c r="Y45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z45" s="9" t="n">
-        <v>0</v>
+      <c r="Z45" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA45" s="10" t="n">
         <v>1</v>
@@ -5976,7 +5976,7 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>10</v>
@@ -6017,10 +6017,10 @@
         </is>
       </c>
       <c r="P52" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q52" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="Q52" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R52" s="9" t="n">
         <v>0</v>
@@ -6046,8 +6046,8 @@
       <c r="Y52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z52" s="9" t="n">
-        <v>0</v>
+      <c r="Z52" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA52" s="10" t="n">
         <v>1</v>
@@ -6297,13 +6297,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>0</v>
       </c>
       <c r="V55" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W55" s="9" t="n">
         <v>0</v>
@@ -6489,7 +6489,7 @@
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6559,8 +6559,8 @@
       <c r="Y57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z57" s="9" t="n">
-        <v>0</v>
+      <c r="Z57" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA57" s="10" t="n">
         <v>1</v>
@@ -6796,7 +6796,7 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6810,13 +6810,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
@@ -6854,14 +6854,14 @@
       <c r="U60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V60" s="9" t="n">
-        <v>0</v>
+      <c r="V60" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X60" s="9" t="n">
-        <v>1</v>
+      <c r="X60" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y60" s="9" t="n">
         <v>0</v>
@@ -7204,7 +7204,7 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -7274,8 +7274,8 @@
       <c r="Y64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z64" s="9" t="n">
-        <v>0</v>
+      <c r="Z64" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA64" s="10" t="n">
         <v>1</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -7375,8 +7375,8 @@
       <c r="Y65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z65" s="9" t="n">
-        <v>0</v>
+      <c r="Z65" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA65" s="10" t="n">
         <v>1</v>
@@ -7406,7 +7406,7 @@
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>10</v>
@@ -7458,11 +7458,11 @@
       <c r="S66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T66" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U66" s="9" t="n">
-        <v>0</v>
+      <c r="T66" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V66" s="9" t="n">
         <v>0</v>
@@ -8420,7 +8420,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8434,13 +8434,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
@@ -8478,11 +8478,11 @@
       <c r="U76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V76" s="9" t="n">
-        <v>0</v>
+      <c r="V76" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W76" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X76" s="10" t="n">
         <v>5</v>
@@ -8490,8 +8490,8 @@
       <c r="Y76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z76" s="9" t="n">
-        <v>0</v>
+      <c r="Z76" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA76" s="10" t="n">
         <v>1</v>
@@ -8993,8 +8993,8 @@
       <c r="W81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X81" s="9" t="n">
-        <v>0</v>
+      <c r="X81" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y81" s="9" t="n">
         <v>0</v>
@@ -9094,8 +9094,8 @@
       <c r="W82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X82" s="9" t="n">
-        <v>0</v>
+      <c r="X82" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y82" s="9" t="n">
         <v>0</v>
@@ -9232,7 +9232,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -9246,13 +9246,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="7" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>1</v>
       </c>
       <c r="V84" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W84" s="9" t="n">
         <v>0</v>
@@ -9302,8 +9302,8 @@
       <c r="Y84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z84" s="9" t="n">
-        <v>0</v>
+      <c r="Z84" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA84" s="10" t="n">
         <v>1</v>
@@ -9333,7 +9333,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -9403,8 +9403,8 @@
       <c r="Y85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z85" s="9" t="n">
-        <v>0</v>
+      <c r="Z85" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA85" s="10" t="n">
         <v>1</v>
@@ -9434,7 +9434,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9504,8 +9504,8 @@
       <c r="Y86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z86" s="9" t="n">
-        <v>0</v>
+      <c r="Z86" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA86" s="10" t="n">
         <v>1</v>
@@ -9599,8 +9599,8 @@
       <c r="W87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X87" s="9" t="n">
-        <v>0</v>
+      <c r="X87" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y87" s="9" t="n">
         <v>0</v>
@@ -9700,8 +9700,8 @@
       <c r="W88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X88" s="9" t="n">
-        <v>0</v>
+      <c r="X88" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y88" s="9" t="n">
         <v>0</v>
@@ -9737,7 +9737,7 @@
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9807,8 +9807,8 @@
       <c r="Y89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z89" s="9" t="n">
-        <v>0</v>
+      <c r="Z89" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA89" s="10" t="n">
         <v>1</v>
@@ -9852,13 +9852,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>4</v>
       </c>
       <c r="W90" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X90" s="10" t="n">
         <v>5</v>
@@ -10044,7 +10044,7 @@
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -10114,8 +10114,8 @@
       <c r="Y92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z92" s="9" t="n">
-        <v>0</v>
+      <c r="Z92" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA92" s="10" t="n">
         <v>1</v>
@@ -10246,7 +10246,7 @@
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -10316,8 +10316,8 @@
       <c r="Y94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z94" s="9" t="n">
-        <v>0</v>
+      <c r="Z94" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA94" s="10" t="n">
         <v>1</v>
@@ -10446,7 +10446,7 @@
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -10516,8 +10516,8 @@
       <c r="Y96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z96" s="9" t="n">
-        <v>0</v>
+      <c r="Z96" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA96" s="10" t="n">
         <v>1</v>
@@ -12494,7 +12494,7 @@
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -12564,8 +12564,8 @@
       <c r="Y116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z116" s="9" t="n">
-        <v>0</v>
+      <c r="Z116" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA116" s="10" t="n">
         <v>1</v>
@@ -12898,7 +12898,7 @@
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -12968,8 +12968,8 @@
       <c r="Y120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z120" s="9" t="n">
-        <v>0</v>
+      <c r="Z120" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA120" s="10" t="n">
         <v>1</v>
@@ -13706,7 +13706,7 @@
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13776,8 +13776,8 @@
       <c r="Y128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z128" s="9" t="n">
-        <v>0</v>
+      <c r="Z128" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA128" s="10" t="n">
         <v>1</v>
@@ -14524,7 +14524,7 @@
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -14594,8 +14594,8 @@
       <c r="Y136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z136" s="9" t="n">
-        <v>0</v>
+      <c r="Z136" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA136" s="10" t="n">
         <v>1</v>
@@ -14831,7 +14831,7 @@
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F139" s="6" t="n">
         <v>10</v>
@@ -14872,7 +14872,7 @@
         </is>
       </c>
       <c r="P139" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q139" s="9" t="n">
         <v>0</v>
@@ -14901,8 +14901,8 @@
       <c r="Y139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z139" s="9" t="n">
-        <v>0</v>
+      <c r="Z139" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA139" s="10" t="n">
         <v>1</v>
@@ -15247,7 +15247,7 @@
         </is>
       </c>
       <c r="E143" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F143" s="6" t="n">
         <v>10</v>
@@ -15317,8 +15317,8 @@
       <c r="Y143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z143" s="9" t="n">
-        <v>0</v>
+      <c r="Z143" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA143" s="10" t="n">
         <v>1</v>
@@ -15348,7 +15348,7 @@
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F144" s="6" t="n">
         <v>10</v>
@@ -15418,8 +15418,8 @@
       <c r="Y144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z144" s="9" t="n">
-        <v>0</v>
+      <c r="Z144" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA144" s="10" t="n">
         <v>1</v>
@@ -15554,7 +15554,7 @@
         </is>
       </c>
       <c r="E146" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F146" s="6" t="n">
         <v>10</v>
@@ -15610,7 +15610,7 @@
         <v>1</v>
       </c>
       <c r="U146" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V146" s="9" t="n">
         <v>0</v>
@@ -15624,8 +15624,8 @@
       <c r="Y146" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z146" s="9" t="n">
-        <v>0</v>
+      <c r="Z146" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA146" s="10" t="n">
         <v>1</v>
@@ -15723,7 +15723,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -15756,7 +15756,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -15789,7 +15789,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -15804,7 +15804,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -15822,7 +15822,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -15888,7 +15888,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -15921,7 +15921,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -15954,7 +15954,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -16020,7 +16020,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -16053,7 +16053,7 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -16086,7 +16086,7 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -16152,7 +16152,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -16185,7 +16185,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -16218,7 +16218,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -16284,7 +16284,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -16317,7 +16317,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -16350,7 +16350,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -16383,7 +16383,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -16581,7 +16581,7 @@
         <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -16614,7 +16614,7 @@
         <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -16680,7 +16680,7 @@
         <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
         <v>2</v>
@@ -16713,7 +16713,7 @@
         <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -16746,7 +16746,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="E33" t="n">
         <v>1</v>
@@ -16779,13 +16779,13 @@
         <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>

--- a/docs/d/79/inyear.xlsx
+++ b/docs/d/79/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 27 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 27 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 71 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 69 clubs short</t>
         </is>
       </c>
     </row>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -963,17 +963,17 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M3" s="8" t="n">
@@ -1008,7 +1008,7 @@
         <v>0</v>
       </c>
       <c r="V3" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W3" s="9" t="n">
         <v>0</v>
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>43</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>8</v>
+        <v>-12</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>4</v>
       </c>
       <c r="W5" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X5" s="10" t="n">
         <v>6</v>
@@ -1274,17 +1274,17 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M6" s="8" t="n">
@@ -1322,7 +1322,7 @@
         <v>4</v>
       </c>
       <c r="W6" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X6" s="10" t="n">
         <v>6</v>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>10</v>
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
@@ -1408,8 +1408,8 @@
       <c r="P7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Q7" s="9" t="n">
-        <v>1</v>
+      <c r="Q7" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R7" s="9" t="n">
         <v>0</v>
@@ -1480,17 +1480,17 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M8" s="8" t="n">
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="P8" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q8" s="9" t="n">
         <v>1</v>
@@ -1585,17 +1585,17 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M9" s="8" t="n">
@@ -1690,17 +1690,17 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-17</v>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M10" s="8" t="n">
@@ -1795,17 +1795,17 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-17</v>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M11" s="8" t="n">
@@ -1886,7 +1886,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>10</v>
@@ -1900,17 +1900,17 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M12" s="8" t="n">
@@ -1944,11 +1944,11 @@
       <c r="U12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V12" s="9" t="n">
-        <v>1</v>
+      <c r="V12" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W12" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X12" s="10" t="n">
         <v>4</v>
@@ -2001,13 +2001,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -2102,17 +2102,17 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M14" s="8" t="n">
@@ -2207,13 +2207,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-5</v>
+        <v>-16</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
@@ -2308,13 +2308,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>0</v>
       </c>
       <c r="V16" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W16" s="9" t="n">
         <v>0</v>
@@ -2409,17 +2409,17 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-16</v>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M17" s="8" t="n">
@@ -2514,13 +2514,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
@@ -2615,13 +2615,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -2716,13 +2716,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>0</v>
       </c>
       <c r="V20" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W20" s="9" t="n">
         <v>0</v>
@@ -2821,13 +2821,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>4</v>
       </c>
       <c r="W21" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X21" s="10" t="n">
         <v>7</v>
@@ -2912,7 +2912,7 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>10</v>
@@ -2926,13 +2926,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
@@ -2970,11 +2970,11 @@
       <c r="U22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V22" s="9" t="n">
-        <v>2</v>
+      <c r="V22" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W22" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X22" s="10" t="n">
         <v>4</v>
@@ -3027,17 +3027,17 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-27</v>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M23" s="8" t="n">
@@ -3128,17 +3128,17 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-16</v>
+      </c>
+      <c r="L24" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M24" s="8" t="n">
@@ -3233,13 +3233,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
@@ -3334,13 +3334,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>8</v>
+        <v>-2</v>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>2</v>
       </c>
       <c r="R26" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" s="9" t="n">
         <v>1</v>
@@ -3382,7 +3382,7 @@
         <v>4</v>
       </c>
       <c r="W26" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X26" s="10" t="n">
         <v>6</v>
@@ -3439,13 +3439,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>4</v>
       </c>
       <c r="W27" s="10" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="X27" s="10" t="n">
         <v>7</v>
@@ -3544,17 +3544,17 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L28" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M28" s="8" t="n">
@@ -3649,17 +3649,17 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>57</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-42</v>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M29" s="8" t="n">
@@ -3694,7 +3694,7 @@
         <v>0</v>
       </c>
       <c r="V29" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W29" s="9" t="n">
         <v>0</v>
@@ -3740,7 +3740,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3810,8 +3810,8 @@
       <c r="Y30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z30" s="9" t="n">
-        <v>0</v>
+      <c r="Z30" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA30" s="10" t="n">
         <v>1</v>
@@ -3853,13 +3853,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -3954,17 +3954,17 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L32" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L32" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M32" s="8" t="n">
@@ -4002,7 +4002,7 @@
         <v>4</v>
       </c>
       <c r="W32" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X32" s="10" t="n">
         <v>4</v>
@@ -4055,17 +4055,17 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L33" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L33" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M33" s="8" t="n">
@@ -4160,17 +4160,17 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L34" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M34" s="8" t="n">
@@ -4261,13 +4261,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>10</v>
@@ -4362,13 +4362,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>5</v>
+        <v>-6</v>
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
@@ -4400,8 +4400,8 @@
       <c r="S36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T36" s="9" t="n">
-        <v>0</v>
+      <c r="T36" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U36" s="9" t="n">
         <v>0</v>
@@ -4409,8 +4409,8 @@
       <c r="V36" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W36" s="9" t="n">
-        <v>1</v>
+      <c r="W36" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="X36" s="10" t="n">
         <v>7</v>
@@ -4568,13 +4568,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
@@ -4669,13 +4669,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F40" s="6" t="n">
         <v>10</v>
@@ -4770,13 +4770,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
@@ -4814,8 +4814,8 @@
       <c r="U40" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="V40" s="9" t="n">
-        <v>2</v>
+      <c r="V40" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W40" s="9" t="n">
         <v>0</v>
@@ -4871,17 +4871,17 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L41" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L41" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M41" s="8" t="n">
@@ -4919,7 +4919,7 @@
         <v>4</v>
       </c>
       <c r="W41" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X41" s="10" t="n">
         <v>6</v>
@@ -4972,17 +4972,17 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L42" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L42" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M42" s="8" t="n">
@@ -5020,7 +5020,7 @@
         <v>4</v>
       </c>
       <c r="W42" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X42" s="10" t="n">
         <v>4</v>
@@ -5077,13 +5077,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
         <v>0</v>
       </c>
       <c r="V43" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W43" s="9" t="n">
         <v>0</v>
@@ -5178,13 +5178,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
@@ -5279,13 +5279,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -5380,13 +5380,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>3</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
@@ -5582,13 +5582,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
@@ -5683,13 +5683,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
@@ -5784,13 +5784,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -5889,13 +5889,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
@@ -5990,13 +5990,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         <v>0</v>
       </c>
       <c r="V52" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W52" s="9" t="n">
         <v>0</v>
@@ -6283,7 +6283,7 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>10</v>
@@ -6297,13 +6297,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
@@ -6333,16 +6333,16 @@
         <v>0</v>
       </c>
       <c r="S55" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T55" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="T55" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V55" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W55" s="9" t="n">
         <v>0</v>
@@ -6398,17 +6398,17 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L56" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L56" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M56" s="8" t="n">
@@ -6443,7 +6443,7 @@
         <v>0</v>
       </c>
       <c r="V56" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W56" s="9" t="n">
         <v>0</v>
@@ -6503,17 +6503,17 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="L57" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L57" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M57" s="8" t="n">
@@ -6604,13 +6604,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
@@ -6705,17 +6705,17 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-23</v>
+      </c>
+      <c r="L59" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M59" s="8" t="n">
@@ -6796,7 +6796,7 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6810,13 +6810,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
@@ -6836,23 +6836,23 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P60" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S60" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U60" s="9" t="n">
-        <v>0</v>
+      <c r="P60" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q60" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R60" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S60" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T60" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" s="10" t="n">
+        <v>8</v>
       </c>
       <c r="V60" s="10" t="n">
         <v>4</v>
@@ -6911,13 +6911,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -7012,13 +7012,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         <v>0</v>
       </c>
       <c r="V62" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W62" s="9" t="n">
         <v>0</v>
@@ -7099,7 +7099,7 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -7113,13 +7113,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>3</v>
+        <v>-8</v>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
@@ -7143,13 +7143,13 @@
         <v>3</v>
       </c>
       <c r="Q63" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S63" s="9" t="n">
-        <v>1</v>
+      <c r="S63" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T63" s="10" t="n">
         <v>1</v>
@@ -7157,11 +7157,11 @@
       <c r="U63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V63" s="9" t="n">
-        <v>3</v>
+      <c r="V63" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W63" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X63" s="10" t="n">
         <v>6</v>
@@ -7218,13 +7218,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>0</v>
       </c>
       <c r="V65" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W65" s="9" t="n">
         <v>0</v>
@@ -7420,17 +7420,17 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L66" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M66" s="8" t="n">
@@ -7525,13 +7525,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
@@ -7727,13 +7727,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
@@ -7828,17 +7828,17 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-26</v>
+      </c>
+      <c r="L70" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M70" s="8" t="n">
@@ -8030,13 +8030,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -8232,13 +8232,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F75" s="6" t="n">
         <v>10</v>
@@ -8333,13 +8333,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>0</v>
       </c>
       <c r="V75" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W75" s="9" t="n">
         <v>0</v>
@@ -8389,8 +8389,8 @@
       <c r="Y75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z75" s="9" t="n">
-        <v>0</v>
+      <c r="Z75" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="AA75" s="10" t="n">
         <v>1</v>
@@ -8434,13 +8434,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
@@ -8482,7 +8482,7 @@
         <v>4</v>
       </c>
       <c r="W76" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X76" s="10" t="n">
         <v>5</v>
@@ -8535,13 +8535,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
@@ -8636,13 +8636,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
@@ -8741,13 +8741,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
@@ -8842,13 +8842,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
@@ -8943,13 +8943,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
@@ -9145,13 +9145,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
@@ -9246,13 +9246,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L84" s="7" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>1</v>
       </c>
       <c r="V84" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W84" s="9" t="n">
         <v>0</v>
@@ -9392,7 +9392,7 @@
         <v>0</v>
       </c>
       <c r="V85" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W85" s="9" t="n">
         <v>0</v>
@@ -9549,13 +9549,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
@@ -9650,13 +9650,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="L88" s="7" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9751,13 +9751,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -9795,11 +9795,11 @@
       <c r="U89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V89" s="9" t="n">
-        <v>0</v>
+      <c r="V89" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X89" s="10" t="n">
         <v>5</v>
@@ -9838,7 +9838,7 @@
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -9852,13 +9852,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>7</v>
+        <v>-3</v>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
@@ -9899,8 +9899,8 @@
       <c r="V90" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W90" s="9" t="n">
-        <v>3</v>
+      <c r="W90" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X90" s="10" t="n">
         <v>5</v>
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
@@ -10058,13 +10058,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>43</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
@@ -10159,13 +10159,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         </is>
       </c>
       <c r="P93" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q93" s="9" t="n">
         <v>1</v>
@@ -10246,7 +10246,7 @@
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -10260,13 +10260,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -10304,11 +10304,11 @@
       <c r="U94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V94" s="9" t="n">
-        <v>0</v>
+      <c r="V94" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W94" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X94" s="10" t="n">
         <v>6</v>
@@ -10561,13 +10561,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>10</v>
+        <v>-2</v>
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
         <v>0</v>
       </c>
       <c r="V98" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W98" s="9" t="n">
         <v>0</v>
@@ -10771,17 +10771,17 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L99" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M99" s="8" t="n">
@@ -10816,7 +10816,7 @@
         <v>0</v>
       </c>
       <c r="V99" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W99" s="9" t="n">
         <v>0</v>
@@ -10876,13 +10876,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         <v>4</v>
       </c>
       <c r="W100" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X100" s="10" t="n">
         <v>4</v>
@@ -10977,13 +10977,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
         <v>0</v>
       </c>
       <c r="V101" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W101" s="9" t="n">
         <v>0</v>
@@ -11078,13 +11078,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
@@ -11179,13 +11179,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
@@ -11280,13 +11280,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L104" s="7" t="inlineStr">
         <is>
@@ -11583,17 +11583,17 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L107" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L107" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M107" s="8" t="n">
@@ -11688,17 +11688,17 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-21</v>
+      </c>
+      <c r="L108" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M108" s="8" t="n">
@@ -11789,17 +11789,17 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L109" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L109" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M109" s="8" t="n">
@@ -11837,7 +11837,7 @@
         <v>4</v>
       </c>
       <c r="W109" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X109" s="10" t="n">
         <v>6</v>
@@ -11894,13 +11894,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
@@ -11921,7 +11921,7 @@
         </is>
       </c>
       <c r="P110" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q110" s="9" t="n">
         <v>0</v>
@@ -11999,13 +11999,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
@@ -12104,13 +12104,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L112" s="7" t="inlineStr">
         <is>
@@ -12205,13 +12205,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
@@ -12306,13 +12306,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
@@ -12407,13 +12407,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
@@ -12508,17 +12508,17 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L116" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L116" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M116" s="8" t="n">
@@ -12609,13 +12609,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
@@ -12710,13 +12710,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L118" s="7" t="inlineStr">
         <is>
@@ -12811,13 +12811,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -12912,13 +12912,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L120" s="7" t="inlineStr">
         <is>
@@ -12956,8 +12956,8 @@
       <c r="U120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V120" s="9" t="n">
-        <v>0</v>
+      <c r="V120" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W120" s="9" t="n">
         <v>0</v>
@@ -13013,17 +13013,17 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L121" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L121" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M121" s="8" t="n">
@@ -13114,13 +13114,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L122" s="7" t="inlineStr">
         <is>
@@ -13215,13 +13215,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
@@ -13316,13 +13316,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
@@ -13417,13 +13417,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
@@ -13518,13 +13518,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L126" s="7" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13720,17 +13720,17 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L128" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L128" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M128" s="8" t="n">
@@ -13749,11 +13749,11 @@
       <c r="P128" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="Q128" s="9" t="n">
-        <v>1</v>
+      <c r="Q128" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R128" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S128" s="9" t="n">
         <v>0</v>
@@ -13764,11 +13764,11 @@
       <c r="U128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V128" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W128" s="9" t="n">
-        <v>0</v>
+      <c r="V128" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W128" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="X128" s="10" t="n">
         <v>4</v>
@@ -13821,13 +13821,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="L129" s="4" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         <v>4</v>
       </c>
       <c r="W129" s="10" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="X129" s="10" t="n">
         <v>6</v>
@@ -14025,13 +14025,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
@@ -14112,7 +14112,7 @@
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>10</v>
@@ -14126,13 +14126,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>15</v>
+        <v>-1</v>
       </c>
       <c r="L132" s="4" t="inlineStr">
         <is>
@@ -14158,8 +14158,8 @@
       <c r="Q132" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R132" s="9" t="n">
-        <v>0</v>
+      <c r="R132" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S132" s="9" t="n">
         <v>0</v>
@@ -14167,14 +14167,14 @@
       <c r="T132" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U132" s="9" t="n">
-        <v>0</v>
+      <c r="U132" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V132" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W132" s="10" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="X132" s="10" t="n">
         <v>5</v>
@@ -14217,7 +14217,7 @@
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -14231,13 +14231,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L133" s="7" t="inlineStr">
         <is>
@@ -14275,11 +14275,11 @@
       <c r="U133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V133" s="9" t="n">
-        <v>1</v>
+      <c r="V133" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W133" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X133" s="9" t="n">
         <v>1</v>
@@ -14332,13 +14332,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>41</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>13</v>
+        <v>-7</v>
       </c>
       <c r="L134" s="4" t="inlineStr">
         <is>
@@ -14380,7 +14380,7 @@
         <v>4</v>
       </c>
       <c r="W134" s="10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X134" s="10" t="n">
         <v>4</v>
@@ -14437,13 +14437,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L135" s="7" t="inlineStr">
         <is>
@@ -14538,13 +14538,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L136" s="7" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
         <v>4</v>
       </c>
       <c r="Q136" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R136" s="9" t="n">
         <v>0</v>
@@ -14639,13 +14639,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>16</v>
+        <v>-2</v>
       </c>
       <c r="L137" s="4" t="inlineStr">
         <is>
@@ -14687,7 +14687,7 @@
         <v>4</v>
       </c>
       <c r="W137" s="10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X137" s="10" t="n">
         <v>4</v>
@@ -14744,13 +14744,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L138" s="7" t="inlineStr">
         <is>
@@ -14845,13 +14845,13 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L139" s="4" t="inlineStr">
         <is>
@@ -14893,7 +14893,7 @@
         <v>4</v>
       </c>
       <c r="W139" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X139" s="10" t="n">
         <v>5</v>
@@ -14932,7 +14932,7 @@
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F140" s="6" t="n">
         <v>10</v>
@@ -14946,17 +14946,17 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L140" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L140" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M140" s="8" t="n">
@@ -14993,8 +14993,8 @@
       <c r="V140" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W140" s="9" t="n">
-        <v>0</v>
+      <c r="W140" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X140" s="10" t="n">
         <v>4</v>
@@ -15051,13 +15051,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>10</v>
+        <v>-9</v>
       </c>
       <c r="L141" s="4" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F142" s="6" t="n">
         <v>10</v>
@@ -15156,13 +15156,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>7</v>
+        <v>-8</v>
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
@@ -15183,7 +15183,7 @@
         </is>
       </c>
       <c r="P142" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q142" s="10" t="n">
         <v>2</v>
@@ -15203,8 +15203,8 @@
       <c r="V142" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W142" s="9" t="n">
-        <v>3</v>
+      <c r="W142" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X142" s="10" t="n">
         <v>6</v>
@@ -15261,17 +15261,17 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="L143" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L143" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M143" s="8" t="n">
@@ -15309,7 +15309,7 @@
         <v>4</v>
       </c>
       <c r="W143" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X143" s="10" t="n">
         <v>4</v>
@@ -15348,7 +15348,7 @@
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F144" s="6" t="n">
         <v>10</v>
@@ -15362,17 +15362,17 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L144" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L144" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M144" s="8" t="n">
@@ -15406,8 +15406,8 @@
       <c r="U144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V144" s="9" t="n">
-        <v>3</v>
+      <c r="V144" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W144" s="9" t="n">
         <v>0</v>
@@ -15467,13 +15467,13 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L145" s="7" t="inlineStr">
         <is>
@@ -15568,13 +15568,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J146" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L146" s="7" t="inlineStr">
         <is>
@@ -15613,7 +15613,7 @@
         <v>3</v>
       </c>
       <c r="V146" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W146" s="9" t="n">
         <v>0</v>
@@ -15738,7 +15738,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -15756,7 +15756,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -15771,7 +15771,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -15789,7 +15789,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -15804,7 +15804,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -15837,7 +15837,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -15888,7 +15888,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -15903,7 +15903,7 @@
         <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -15921,7 +15921,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -15936,7 +15936,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -15969,7 +15969,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -15987,7 +15987,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -16035,7 +16035,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -16086,7 +16086,7 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>0.67</v>
+        <v>1.17</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -16101,7 +16101,7 @@
         <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -16119,13 +16119,13 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -16134,7 +16134,7 @@
         <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -16152,7 +16152,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -16200,7 +16200,7 @@
         <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -16218,7 +16218,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -16350,13 +16350,13 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -16383,7 +16383,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -16431,7 +16431,7 @@
         <v>2</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -16497,7 +16497,7 @@
         <v>2</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -16530,7 +16530,7 @@
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -16596,7 +16596,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -16614,7 +16614,7 @@
         <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -16629,7 +16629,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -16680,13 +16680,13 @@
         <v>6</v>
       </c>
       <c r="D31" t="n">
+        <v>4</v>
+      </c>
+      <c r="E31" t="n">
         <v>3</v>
       </c>
-      <c r="E31" t="n">
-        <v>2</v>
-      </c>
       <c r="F31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -16695,7 +16695,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -16746,7 +16746,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="E33" t="n">
         <v>1</v>
@@ -16761,7 +16761,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -16779,7 +16779,7 @@
         <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="E34" t="n">
         <v>2</v>
@@ -16794,7 +16794,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/79/inyear.xlsx
+++ b/docs/d/79/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/79/inyear.xlsx
+++ b/docs/d/79/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/79/inyear.xlsx
+++ b/docs/d/79/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/79/inyear.xlsx
+++ b/docs/d/79/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/79/inyear.xlsx
+++ b/docs/d/79/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 27 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 27 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 69 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 69 clubs short</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>10</v>
@@ -1001,8 +1001,8 @@
       <c r="S3" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T3" s="9" t="n">
-        <v>0</v>
+      <c r="T3" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U3" s="9" t="n">
         <v>0</v>
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>43</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>10</v>
@@ -1405,14 +1405,14 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P7" s="9" t="n">
-        <v>3</v>
+      <c r="P7" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q7" s="10" t="n">
         <v>2</v>
       </c>
       <c r="R7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" s="9" t="n">
         <v>0</v>
@@ -2308,13 +2308,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>0</v>
       </c>
       <c r="V16" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W16" s="9" t="n">
         <v>0</v>
@@ -2409,13 +2409,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-16</v>
+        <v>-13</v>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>1</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" s="9" t="n">
         <v>0</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>10</v>
@@ -2821,13 +2821,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
@@ -2847,8 +2847,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P21" s="9" t="n">
-        <v>3</v>
+      <c r="P21" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q21" s="10" t="n">
         <v>2</v>
@@ -2869,7 +2869,7 @@
         <v>4</v>
       </c>
       <c r="W21" s="10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="X21" s="10" t="n">
         <v>7</v>
@@ -3439,13 +3439,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>4</v>
       </c>
       <c r="W27" s="10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X27" s="10" t="n">
         <v>7</v>
@@ -4972,13 +4972,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>4</v>
       </c>
       <c r="W42" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X42" s="10" t="n">
         <v>4</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
@@ -9852,13 +9852,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>4</v>
       </c>
       <c r="W90" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X90" s="10" t="n">
         <v>5</v>
@@ -10159,13 +10159,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10666,13 +10666,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
@@ -10710,11 +10710,11 @@
       <c r="U98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V98" s="9" t="n">
-        <v>3</v>
+      <c r="V98" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W98" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X98" s="10" t="n">
         <v>7</v>
@@ -10862,7 +10862,7 @@
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10876,13 +10876,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
@@ -10923,8 +10923,8 @@
       <c r="V100" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W100" s="9" t="n">
-        <v>3</v>
+      <c r="W100" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X100" s="10" t="n">
         <v>4</v>
@@ -11280,13 +11280,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J104" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L104" s="7" t="inlineStr">
         <is>
@@ -14025,13 +14025,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
@@ -14159,7 +14159,7 @@
         <v>2</v>
       </c>
       <c r="R132" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S132" s="9" t="n">
         <v>0</v>
@@ -14332,13 +14332,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>41</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="L134" s="4" t="inlineStr">
         <is>
@@ -14380,7 +14380,7 @@
         <v>4</v>
       </c>
       <c r="W134" s="10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="X134" s="10" t="n">
         <v>4</v>
@@ -14639,13 +14639,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L137" s="4" t="inlineStr">
         <is>
@@ -14687,7 +14687,7 @@
         <v>4</v>
       </c>
       <c r="W137" s="10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="X137" s="10" t="n">
         <v>4</v>
@@ -14872,7 +14872,7 @@
         </is>
       </c>
       <c r="P139" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q139" s="9" t="n">
         <v>0</v>
@@ -14946,13 +14946,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="L140" s="7" t="inlineStr">
         <is>
@@ -15261,13 +15261,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -15756,7 +15756,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -16416,7 +16416,7 @@
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>

--- a/docs/d/79/inyear.xlsx
+++ b/docs/d/79/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 27 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 27 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 69 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 69 clubs short</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>10</v>
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -1007,8 +1007,8 @@
       <c r="U3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V3" s="9" t="n">
-        <v>3</v>
+      <c r="V3" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W3" s="9" t="n">
         <v>0</v>
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>43</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-11</v>
+        <v>-7</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>4</v>
       </c>
       <c r="W5" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X5" s="10" t="n">
         <v>6</v>
@@ -1304,7 +1304,7 @@
         <v>0</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" s="9" t="n">
         <v>0</v>
@@ -1406,7 +1406,7 @@
         </is>
       </c>
       <c r="P7" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q7" s="10" t="n">
         <v>2</v>
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="P9" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q9" s="9" t="n">
         <v>0</v>
@@ -6017,7 +6017,7 @@
         </is>
       </c>
       <c r="P52" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q52" s="10" t="n">
         <v>2</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
@@ -6551,7 +6551,7 @@
         <v>4</v>
       </c>
       <c r="W57" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X57" s="10" t="n">
         <v>5</v>
@@ -7727,13 +7727,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>1</v>
       </c>
       <c r="U90" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V90" s="10" t="n">
         <v>4</v>
@@ -10460,13 +10460,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
@@ -10505,7 +10505,7 @@
         <v>0</v>
       </c>
       <c r="V96" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W96" s="9" t="n">
         <v>0</v>
@@ -10666,13 +10666,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>0</v>
       </c>
       <c r="Q98" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R98" s="9" t="n">
         <v>0</v>
@@ -14112,7 +14112,7 @@
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>10</v>
@@ -14152,8 +14152,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P132" s="9" t="n">
-        <v>3</v>
+      <c r="P132" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q132" s="10" t="n">
         <v>2</v>
@@ -14666,7 +14666,7 @@
         </is>
       </c>
       <c r="P137" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q137" s="9" t="n">
         <v>1</v>
@@ -14976,7 +14976,7 @@
         <v>1</v>
       </c>
       <c r="Q140" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R140" s="9" t="n">
         <v>0</v>
@@ -15595,7 +15595,7 @@
         </is>
       </c>
       <c r="P146" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q146" s="10" t="n">
         <v>2</v>
@@ -15604,7 +15604,7 @@
         <v>0</v>
       </c>
       <c r="S146" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T146" s="10" t="n">
         <v>1</v>
@@ -15723,7 +15723,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -16680,7 +16680,7 @@
         <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
+        <v>4.17</v>
       </c>
       <c r="E31" t="n">
         <v>3</v>
